--- a/data/results/LP-basedBounds.xlsx
+++ b/data/results/LP-basedBounds.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Comparison" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Comparison!$A$4:$AD$52</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Comparison!$A$4:$Y$52</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Instances!$A$3:$F$51</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -240,10 +240,10 @@
     <t xml:space="preserve">CG</t>
   </si>
   <si>
+    <t xml:space="preserve">F1</t>
+  </si>
+  <si>
     <t xml:space="preserve">F11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F1</t>
   </si>
   <si>
     <t xml:space="preserve">Sets</t>
@@ -395,14 +395,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4CCCC"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -487,164 +487,168 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -657,7 +661,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -700,14 +704,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFD6E4F0"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -733,14 +729,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFE2EFDA"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1008,1001 +996,1001 @@
   <dimension ref="A1:F51"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="6" t="n">
         <v>14834</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>0.745427135678392</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="8" t="n">
         <v>21230</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C5" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="11" t="n">
         <v>9876</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="12" t="n">
         <v>0.496281407035176</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="8" t="n">
         <v>6542</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <v>12048</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>0.605427135678392</v>
       </c>
-      <c r="F6" s="7" t="n">
+      <c r="F6" s="8" t="n">
         <v>10303</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="11" t="n">
         <v>13089</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>0.657738693467337</v>
       </c>
-      <c r="F7" s="7" t="n">
+      <c r="F7" s="8" t="n">
         <v>13967</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="6" t="n">
         <v>59681</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>0.747882205513785</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="8" t="n">
         <v>46785</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="11" t="n">
         <v>400</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="11" t="n">
         <v>59765</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <v>0.748934837092732</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="F9" s="8" t="n">
         <v>54304</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>125</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="6" t="n">
         <v>6963</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <v>0.898451612903226</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="8" t="n">
         <v>66248</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="11" t="n">
         <v>1534</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="12" t="n">
         <v>0.0770854271356784</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="8" t="n">
         <v>7734</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="6" t="n">
         <v>3235</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>0.162562814070352</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="8" t="n">
         <v>26389</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="11" t="n">
         <v>8473</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="12" t="n">
         <v>0.425778894472362</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="8" t="n">
         <v>168200</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="6" t="n">
         <v>4459</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>0.0357434869739479</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="8" t="n">
         <v>10738</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="11" t="n">
         <v>9139</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="12" t="n">
         <v>0.0732585170340681</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F15" s="8" t="n">
         <v>38350</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="6" t="n">
         <v>23191</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>0.185899799599198</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="8" t="n">
         <v>205864</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="10" t="n">
+      <c r="C17" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="11" t="n">
         <v>46627</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="12" t="n">
         <v>0.373763527054108</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="8" t="n">
         <v>804000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="6" t="n">
         <v>62624</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="7" t="n">
         <v>0.501995991983968</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="8" t="n">
         <v>9626</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="10" t="n">
+      <c r="C19" s="11" t="n">
         <v>1000</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="11" t="n">
         <v>249826</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="12" t="n">
         <v>0.500152152152152</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="8" t="n">
         <v>12054</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D20" s="6" t="n">
         <v>17910</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="7" t="n">
         <v>0.9</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="8" t="n">
         <v>94362</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="10" t="n">
+      <c r="C21" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="11" t="n">
         <v>17910</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="8" t="n">
         <v>150839</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D22" s="6" t="n">
         <v>1824</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>0.904761904761905</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="8" t="n">
         <v>32736</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="10" t="n">
+      <c r="C23" s="11" t="n">
         <v>64</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="11" t="n">
         <v>704</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E23" s="12" t="n">
         <v>0.349206349206349</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="8" t="n">
         <v>396</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="6" t="n">
         <v>256</v>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="D24" s="6" t="n">
         <v>31616</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="7" t="n">
         <v>0.968627450980392</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F24" s="8" t="n">
         <v>800624</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C25" s="11" t="n">
         <v>256</v>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D25" s="11" t="n">
         <v>20864</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E25" s="12" t="n">
         <v>0.63921568627451</v>
       </c>
-      <c r="F25" s="7" t="n">
+      <c r="F25" s="8" t="n">
         <v>12360</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="D26" s="5" t="n">
+      <c r="D26" s="6" t="n">
         <v>210</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="7" t="n">
         <v>0.555555555555556</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F26" s="8" t="n">
         <v>192</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C27" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D27" s="11" t="n">
         <v>1855</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="12" t="n">
         <v>0.768115942028986</v>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="F27" s="8" t="n">
         <v>6552</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="D28" s="6" t="n">
         <v>5460</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="7" t="n">
         <v>0.764705882352941</v>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="F28" s="8" t="n">
         <v>3808</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="10" t="n">
+      <c r="C29" s="11" t="n">
         <v>171</v>
       </c>
-      <c r="D29" s="10" t="n">
+      <c r="D29" s="11" t="n">
         <v>9435</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E29" s="12" t="n">
         <v>0.649122807017544</v>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="F29" s="8" t="n">
         <v>6745</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="D30" s="6" t="n">
         <v>918</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="7" t="n">
         <v>0.927272727272727</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F30" s="8" t="n">
         <v>5460</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="10" t="n">
+      <c r="C31" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="D31" s="10" t="n">
+      <c r="D31" s="11" t="n">
         <v>10933</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="12" t="n">
         <v>0.243768115942029</v>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="F31" s="8" t="n">
         <v>3321</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C32" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="D32" s="5" t="n">
+      <c r="D32" s="6" t="n">
         <v>21928</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="7" t="n">
         <v>0.48891861761427</v>
       </c>
-      <c r="F32" s="7" t="n">
+      <c r="F32" s="8" t="n">
         <v>31564</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="10" t="n">
+      <c r="C33" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="D33" s="10" t="n">
+      <c r="D33" s="11" t="n">
         <v>33390</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="12" t="n">
         <v>0.744481605351171</v>
       </c>
-      <c r="F33" s="7" t="n">
+      <c r="F33" s="8" t="n">
         <v>63390</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C34" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D34" s="6" t="n">
         <v>31569</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E34" s="7" t="n">
         <v>0.253058116232465</v>
       </c>
-      <c r="F34" s="7" t="n">
+      <c r="F34" s="8" t="n">
         <v>4764</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="10" t="n">
+      <c r="C35" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="D35" s="10" t="n">
+      <c r="D35" s="11" t="n">
         <v>62946</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="12" t="n">
         <v>0.504577154308617</v>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="F35" s="8" t="n">
         <v>63870</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C36" s="6" t="n">
         <v>700</v>
       </c>
-      <c r="D36" s="5" t="n">
+      <c r="D36" s="6" t="n">
         <v>60999</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E36" s="7" t="n">
         <v>0.249331698344574</v>
       </c>
-      <c r="F36" s="7" t="n">
+      <c r="F36" s="8" t="n">
         <v>5185</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="10" t="n">
+      <c r="C37" s="11" t="n">
         <v>1000</v>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="D37" s="11" t="n">
         <v>122253</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="12" t="n">
         <v>0.244750750750751</v>
       </c>
-      <c r="F37" s="7" t="n">
+      <c r="F37" s="8" t="n">
         <v>5436</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C38" s="6" t="n">
         <v>1500</v>
       </c>
-      <c r="D38" s="5" t="n">
+      <c r="D38" s="6" t="n">
         <v>284923</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E38" s="7" t="n">
         <v>0.253433844785413</v>
       </c>
-      <c r="F38" s="7" t="n">
+      <c r="F38" s="8" t="n">
         <v>7135</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="10" t="n">
+      <c r="C39" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D39" s="10" t="n">
+      <c r="D39" s="11" t="n">
         <v>13930</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="E39" s="12" t="n">
         <v>0.7</v>
       </c>
-      <c r="F39" s="7" t="n">
+      <c r="F39" s="8" t="n">
         <v>45295</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="5" t="n">
+      <c r="C40" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D40" s="5" t="n">
+      <c r="D40" s="6" t="n">
         <v>13930</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E40" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="F40" s="7" t="n">
+      <c r="F40" s="8" t="n">
         <v>15073</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="10" t="n">
+      <c r="C41" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D41" s="10" t="n">
+      <c r="D41" s="11" t="n">
         <v>17910</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="F41" s="7" t="n">
+      <c r="F41" s="8" t="n">
         <v>242710</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="5" t="n">
+      <c r="C42" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D42" s="5" t="n">
+      <c r="D42" s="6" t="n">
         <v>17910</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E42" s="7" t="n">
         <v>0.9</v>
       </c>
-      <c r="F42" s="7" t="n">
+      <c r="F42" s="8" t="n">
         <v>178468</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C43" s="10" t="n">
+      <c r="C43" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D43" s="10" t="n">
+      <c r="D43" s="11" t="n">
         <v>17910</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="E43" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="F43" s="7" t="n">
+      <c r="F43" s="8" t="n">
         <v>96764</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C44" s="5" t="n">
+      <c r="C44" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="D44" s="5" t="n">
+      <c r="D44" s="6" t="n">
         <v>39900</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E44" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F44" s="8" t="n">
         <v>7442</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C45" s="10" t="n">
+      <c r="C45" s="11" t="n">
         <v>400</v>
       </c>
-      <c r="D45" s="10" t="n">
+      <c r="D45" s="11" t="n">
         <v>55860</v>
       </c>
-      <c r="E45" s="11" t="n">
+      <c r="E45" s="12" t="n">
         <v>0.7</v>
       </c>
-      <c r="F45" s="7" t="n">
+      <c r="F45" s="8" t="n">
         <v>77719</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="5" t="n">
+      <c r="C46" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="D46" s="5" t="n">
+      <c r="D46" s="6" t="n">
         <v>55860</v>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="F46" s="7" t="n">
+      <c r="F46" s="8" t="n">
         <v>44155</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C47" s="10" t="n">
+      <c r="C47" s="11" t="n">
         <v>400</v>
       </c>
-      <c r="D47" s="10" t="n">
+      <c r="D47" s="11" t="n">
         <v>55860</v>
       </c>
-      <c r="E47" s="11" t="n">
+      <c r="E47" s="12" t="n">
         <v>0.7</v>
       </c>
-      <c r="F47" s="7" t="n">
+      <c r="F47" s="8" t="n">
         <v>24727</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="5" t="n">
+      <c r="C48" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="D48" s="5" t="n">
+      <c r="D48" s="6" t="n">
         <v>250500</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="7" t="n">
         <v>0.501501501501502</v>
       </c>
-      <c r="F48" s="7" t="n">
+      <c r="F48" s="8" t="n">
         <v>10661</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C49" s="10" t="n">
+      <c r="C49" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D49" s="10" t="n">
+      <c r="D49" s="11" t="n">
         <v>13868</v>
       </c>
-      <c r="E49" s="11" t="n">
+      <c r="E49" s="12" t="n">
         <v>0.696884422110553</v>
       </c>
-      <c r="F49" s="7" t="n">
+      <c r="F49" s="8" t="n">
         <v>16398</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C50" s="5" t="n">
+      <c r="C50" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="D50" s="5" t="n">
+      <c r="D50" s="6" t="n">
         <v>39984</v>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" s="7" t="n">
         <v>0.501052631578947</v>
       </c>
-      <c r="F50" s="7" t="n">
+      <c r="F50" s="8" t="n">
         <v>8298</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="10" t="n">
+      <c r="C51" s="11" t="n">
         <v>400</v>
       </c>
-      <c r="D51" s="10" t="n">
+      <c r="D51" s="11" t="n">
         <v>55869</v>
       </c>
-      <c r="E51" s="11" t="n">
+      <c r="E51" s="12" t="n">
         <v>0.700112781954887</v>
       </c>
-      <c r="F51" s="7" t="n">
+      <c r="F51" s="8" t="n">
         <v>22791</v>
       </c>
     </row>
@@ -2030,4601 +2018,4602 @@
   <dimension ref="A1:AD52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="23" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="28" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="23" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="28" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16380" style="0" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13" t="s">
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13" t="s">
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13" t="s">
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13" t="s">
+      <c r="V3" s="14"/>
+      <c r="W3" s="14"/>
+      <c r="X3" s="14"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="AA3" s="13"/>
-      <c r="AB3" s="13"/>
-      <c r="AC3" s="13"/>
-      <c r="AD3" s="13"/>
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="14"/>
+      <c r="AD3" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="14" t="s">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="L4" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="M4" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="N4" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="O4" s="15" t="s">
+      <c r="O4" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="P4" s="16" t="s">
+      <c r="P4" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="Q4" s="16" t="s">
+      <c r="Q4" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="R4" s="16" t="s">
+      <c r="R4" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="S4" s="16" t="s">
+      <c r="S4" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="T4" s="16" t="s">
+      <c r="T4" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="U4" s="17" t="s">
+      <c r="U4" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="V4" s="17" t="s">
+      <c r="V4" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="W4" s="17" t="s">
+      <c r="W4" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="X4" s="17" t="s">
+      <c r="X4" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="Y4" s="17" t="s">
+      <c r="Y4" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="Z4" s="18" t="s">
+      <c r="Z4" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="AA4" s="18" t="s">
+      <c r="AA4" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="AB4" s="18" t="s">
+      <c r="AB4" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="AC4" s="18" t="s">
+      <c r="AC4" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="AD4" s="18" t="s">
+      <c r="AD4" s="19" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>14834</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="8" t="n">
         <v>21230</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="20" t="n">
         <v>55</v>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="20" t="n">
         <v>346395</v>
       </c>
-      <c r="H5" s="20" t="n">
+      <c r="H5" s="21" t="n">
         <v>16.3162976919454</v>
       </c>
-      <c r="I5" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J5" s="22" t="n">
+      <c r="I5" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J5" s="23" t="n">
         <v>0.127019</v>
       </c>
-      <c r="K5" s="23" t="n">
+      <c r="K5" s="24" t="n">
         <v>343</v>
       </c>
-      <c r="L5" s="23" t="n">
+      <c r="L5" s="24" t="n">
         <v>310307</v>
       </c>
-      <c r="M5" s="24" t="n">
+      <c r="M5" s="25" t="n">
         <v>14.6164390014131</v>
       </c>
-      <c r="N5" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O5" s="26" t="n">
+      <c r="N5" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O5" s="27" t="n">
         <v>0.454561</v>
       </c>
-      <c r="P5" s="27" t="n">
+      <c r="P5" s="28" t="n">
         <v>173</v>
       </c>
-      <c r="Q5" s="27" t="n">
+      <c r="Q5" s="28" t="n">
         <v>254273</v>
       </c>
-      <c r="R5" s="28" t="n">
+      <c r="R5" s="29" t="n">
         <v>11.9770607630711</v>
       </c>
-      <c r="S5" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T5" s="30" t="n">
+      <c r="S5" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T5" s="31" t="n">
         <v>15.7863</v>
       </c>
-      <c r="U5" s="31" t="n">
+      <c r="U5" s="32" t="n">
         <v>55</v>
       </c>
       <c r="V5" s="32" t="n">
-        <v>242853</v>
+        <v>745274</v>
       </c>
       <c r="W5" s="33" t="n">
-        <v>11.4391427225624</v>
+        <v>35.1047574187471</v>
       </c>
       <c r="X5" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y5" s="35" t="n">
-        <v>0.647876</v>
+        <v>0.29291</v>
       </c>
       <c r="Z5" s="36" t="n">
         <v>55</v>
       </c>
-      <c r="AA5" s="36" t="n">
-        <v>745274</v>
-      </c>
-      <c r="AB5" s="37" t="n">
-        <v>35.1047574187471</v>
-      </c>
-      <c r="AC5" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD5" s="39" t="n">
-        <v>0.29291</v>
+      <c r="AA5" s="37" t="n">
+        <v>242853</v>
+      </c>
+      <c r="AB5" s="38" t="n">
+        <v>11.4391427225624</v>
+      </c>
+      <c r="AC5" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD5" s="40" t="n">
+        <v>0.647876</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <v>9876</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="8" t="n">
         <v>6542</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="20" t="n">
         <v>34</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="20" t="n">
         <v>139041</v>
       </c>
-      <c r="H6" s="20" t="n">
+      <c r="H6" s="21" t="n">
         <v>21.2535921736472</v>
       </c>
-      <c r="I6" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J6" s="22" t="n">
+      <c r="I6" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J6" s="23" t="n">
         <v>0.105723</v>
       </c>
-      <c r="K6" s="23" t="n">
+      <c r="K6" s="24" t="n">
         <v>213</v>
       </c>
-      <c r="L6" s="23" t="n">
+      <c r="L6" s="24" t="n">
         <v>125760</v>
       </c>
-      <c r="M6" s="24" t="n">
+      <c r="M6" s="25" t="n">
         <v>19.2234790583919</v>
       </c>
-      <c r="N6" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O6" s="26" t="n">
+      <c r="N6" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O6" s="27" t="n">
         <v>0.348417</v>
       </c>
-      <c r="P6" s="27" t="n">
+      <c r="P6" s="28" t="n">
         <v>119</v>
       </c>
-      <c r="Q6" s="27" t="n">
+      <c r="Q6" s="28" t="n">
         <v>97347</v>
       </c>
-      <c r="R6" s="28" t="n">
+      <c r="R6" s="29" t="n">
         <v>14.8803118312443</v>
       </c>
-      <c r="S6" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T6" s="30" t="n">
+      <c r="S6" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T6" s="31" t="n">
         <v>21.5897</v>
       </c>
-      <c r="U6" s="31" t="n">
+      <c r="U6" s="32" t="n">
         <v>34</v>
       </c>
       <c r="V6" s="32" t="n">
-        <v>92879</v>
+        <v>494967</v>
       </c>
       <c r="W6" s="33" t="n">
-        <v>14.1973402629165</v>
+        <v>75.6598899419138</v>
       </c>
       <c r="X6" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y6" s="35" t="n">
-        <v>0.466288</v>
+        <v>0.232146</v>
       </c>
       <c r="Z6" s="36" t="n">
         <v>34</v>
       </c>
-      <c r="AA6" s="36" t="n">
-        <v>494967</v>
-      </c>
-      <c r="AB6" s="37" t="n">
-        <v>75.6598899419138</v>
-      </c>
-      <c r="AC6" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD6" s="39" t="n">
-        <v>0.232146</v>
+      <c r="AA6" s="37" t="n">
+        <v>92879</v>
+      </c>
+      <c r="AB6" s="38" t="n">
+        <v>14.1973402629165</v>
+      </c>
+      <c r="AC6" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD6" s="40" t="n">
+        <v>0.466288</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>12048</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="8" t="n">
         <v>10303</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="20" t="n">
         <v>41</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="20" t="n">
         <v>209408</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="21" t="n">
         <v>20.3249538969232</v>
       </c>
-      <c r="I7" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J7" s="22" t="n">
+      <c r="I7" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="23" t="n">
         <v>0.104342</v>
       </c>
-      <c r="K7" s="23" t="n">
+      <c r="K7" s="24" t="n">
         <v>261</v>
       </c>
-      <c r="L7" s="23" t="n">
+      <c r="L7" s="24" t="n">
         <v>186648</v>
       </c>
-      <c r="M7" s="24" t="n">
+      <c r="M7" s="25" t="n">
         <v>18.1158885761429</v>
       </c>
-      <c r="N7" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O7" s="26" t="n">
+      <c r="N7" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O7" s="27" t="n">
         <v>0.360726</v>
       </c>
-      <c r="P7" s="27" t="n">
+      <c r="P7" s="28" t="n">
         <v>155</v>
       </c>
-      <c r="Q7" s="27" t="n">
+      <c r="Q7" s="28" t="n">
         <v>150738</v>
       </c>
-      <c r="R7" s="28" t="n">
+      <c r="R7" s="29" t="n">
         <v>14.630495972047</v>
       </c>
-      <c r="S7" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T7" s="30" t="n">
+      <c r="S7" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T7" s="31" t="n">
         <v>16.2153</v>
       </c>
-      <c r="U7" s="31" t="n">
+      <c r="U7" s="32" t="n">
         <v>41</v>
       </c>
       <c r="V7" s="32" t="n">
-        <v>136337</v>
+        <v>604606</v>
       </c>
       <c r="W7" s="33" t="n">
-        <v>13.2327477433757</v>
+        <v>58.6825196544696</v>
       </c>
       <c r="X7" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y7" s="35" t="n">
-        <v>0.512334</v>
+        <v>0.251139</v>
       </c>
       <c r="Z7" s="36" t="n">
         <v>41</v>
       </c>
-      <c r="AA7" s="36" t="n">
-        <v>604606</v>
-      </c>
-      <c r="AB7" s="37" t="n">
-        <v>58.6825196544696</v>
-      </c>
-      <c r="AC7" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD7" s="39" t="n">
-        <v>0.251139</v>
+      <c r="AA7" s="37" t="n">
+        <v>136337</v>
+      </c>
+      <c r="AB7" s="38" t="n">
+        <v>13.2327477433757</v>
+      </c>
+      <c r="AC7" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD7" s="40" t="n">
+        <v>0.512334</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="11" t="n">
         <v>13089</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="8" t="n">
         <v>13967</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="20" t="n">
         <v>271661</v>
       </c>
-      <c r="H8" s="20" t="n">
+      <c r="H8" s="21" t="n">
         <v>19.4502040524093</v>
       </c>
-      <c r="I8" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J8" s="22" t="n">
+      <c r="I8" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" s="23" t="n">
         <v>0.126963</v>
       </c>
-      <c r="K8" s="23" t="n">
+      <c r="K8" s="24" t="n">
         <v>292</v>
       </c>
-      <c r="L8" s="23" t="n">
+      <c r="L8" s="24" t="n">
         <v>231582</v>
       </c>
-      <c r="M8" s="24" t="n">
+      <c r="M8" s="25" t="n">
         <v>16.5806543996563</v>
       </c>
-      <c r="N8" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O8" s="26" t="n">
+      <c r="N8" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O8" s="27" t="n">
         <v>0.351596</v>
       </c>
-      <c r="P8" s="27" t="n">
+      <c r="P8" s="28" t="n">
         <v>171</v>
       </c>
-      <c r="Q8" s="32" t="n">
+      <c r="Q8" s="37" t="n">
         <v>184480</v>
       </c>
-      <c r="R8" s="28" t="n">
+      <c r="R8" s="29" t="n">
         <v>13.2082766521085</v>
       </c>
-      <c r="S8" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T8" s="30" t="n">
+      <c r="S8" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T8" s="31" t="n">
         <v>15.9346</v>
       </c>
-      <c r="U8" s="31" t="n">
+      <c r="U8" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="V8" s="31" t="n">
-        <v>198959</v>
+      <c r="V8" s="32" t="n">
+        <v>657976</v>
       </c>
       <c r="W8" s="33" t="n">
-        <v>14.244934488437</v>
+        <v>47.1093291329563</v>
       </c>
       <c r="X8" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y8" s="35" t="n">
-        <v>0.590879</v>
+        <v>0.272874</v>
       </c>
       <c r="Z8" s="36" t="n">
         <v>50</v>
       </c>
       <c r="AA8" s="36" t="n">
-        <v>657976</v>
-      </c>
-      <c r="AB8" s="37" t="n">
-        <v>47.1093291329563</v>
-      </c>
-      <c r="AC8" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD8" s="39" t="n">
-        <v>0.272874</v>
+        <v>198959</v>
+      </c>
+      <c r="AB8" s="38" t="n">
+        <v>14.244934488437</v>
+      </c>
+      <c r="AC8" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD8" s="40" t="n">
+        <v>0.590879</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="6" t="n">
         <v>59681</v>
       </c>
-      <c r="E9" s="7" t="n">
+      <c r="E9" s="8" t="n">
         <v>46785</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="20" t="n">
         <v>98</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="20" t="n">
         <v>1269990</v>
       </c>
-      <c r="H9" s="20" t="n">
+      <c r="H9" s="21" t="n">
         <v>27.1452388586085</v>
       </c>
-      <c r="I9" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J9" s="22" t="n">
+      <c r="I9" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="23" t="n">
         <v>0.719121</v>
       </c>
-      <c r="K9" s="23" t="n">
+      <c r="K9" s="24" t="n">
         <v>603</v>
       </c>
-      <c r="L9" s="23" t="n">
+      <c r="L9" s="24" t="n">
         <v>1118270</v>
       </c>
-      <c r="M9" s="24" t="n">
+      <c r="M9" s="25" t="n">
         <v>23.9023191193759</v>
       </c>
-      <c r="N9" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O9" s="26" t="n">
+      <c r="N9" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O9" s="27" t="n">
         <v>3.31473</v>
       </c>
-      <c r="P9" s="27" t="n">
+      <c r="P9" s="28" t="n">
         <v>260</v>
       </c>
-      <c r="Q9" s="27" t="n">
+      <c r="Q9" s="28" t="n">
         <v>908752</v>
       </c>
-      <c r="R9" s="28" t="n">
+      <c r="R9" s="29" t="n">
         <v>19.4240034198995</v>
       </c>
-      <c r="S9" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T9" s="30" t="n">
+      <c r="S9" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T9" s="31" t="n">
         <v>149.763</v>
       </c>
-      <c r="U9" s="31" t="n">
+      <c r="U9" s="32" t="n">
         <v>98</v>
       </c>
       <c r="V9" s="32" t="n">
-        <v>797684</v>
+        <v>2997280</v>
       </c>
       <c r="W9" s="33" t="n">
-        <v>17.049994656407</v>
+        <v>64.0649780912686</v>
       </c>
       <c r="X9" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y9" s="35" t="n">
-        <v>2.9238</v>
+        <v>1.37638</v>
       </c>
       <c r="Z9" s="36" t="n">
         <v>98</v>
       </c>
-      <c r="AA9" s="36" t="n">
-        <v>2997280</v>
-      </c>
-      <c r="AB9" s="37" t="n">
-        <v>64.0649780912686</v>
-      </c>
-      <c r="AC9" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD9" s="39" t="n">
-        <v>1.37638</v>
+      <c r="AA9" s="37" t="n">
+        <v>797684</v>
+      </c>
+      <c r="AB9" s="38" t="n">
+        <v>17.049994656407</v>
+      </c>
+      <c r="AC9" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD9" s="40" t="n">
+        <v>2.9238</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="11" t="n">
         <v>400</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="11" t="n">
         <v>59765</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E10" s="8" t="n">
         <v>54304</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="20" t="n">
         <v>1286460</v>
       </c>
-      <c r="H10" s="20" t="n">
+      <c r="H10" s="21" t="n">
         <v>23.6899675898645</v>
       </c>
-      <c r="I10" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J10" s="22" t="n">
+      <c r="I10" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10" s="23" t="n">
         <v>0.839636</v>
       </c>
-      <c r="K10" s="23" t="n">
+      <c r="K10" s="24" t="n">
         <v>600</v>
       </c>
-      <c r="L10" s="23" t="n">
+      <c r="L10" s="24" t="n">
         <v>1113340</v>
       </c>
-      <c r="M10" s="24" t="n">
+      <c r="M10" s="25" t="n">
         <v>20.5019888037714</v>
       </c>
-      <c r="N10" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O10" s="26" t="n">
+      <c r="N10" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O10" s="27" t="n">
         <v>2.19514</v>
       </c>
-      <c r="P10" s="27" t="n">
+      <c r="P10" s="28" t="n">
         <v>266</v>
       </c>
-      <c r="Q10" s="27" t="n">
+      <c r="Q10" s="28" t="n">
         <v>904059</v>
       </c>
-      <c r="R10" s="28" t="n">
+      <c r="R10" s="29" t="n">
         <v>16.6481106364172</v>
       </c>
-      <c r="S10" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T10" s="30" t="n">
+      <c r="S10" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T10" s="31" t="n">
         <v>154.02</v>
       </c>
-      <c r="U10" s="31" t="n">
+      <c r="U10" s="32" t="n">
         <v>100</v>
       </c>
       <c r="V10" s="32" t="n">
-        <v>827571</v>
+        <v>3006520</v>
       </c>
       <c r="W10" s="33" t="n">
-        <v>15.2395956098998</v>
+        <v>55.3646140247496</v>
       </c>
       <c r="X10" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y10" s="35" t="n">
-        <v>2.86361</v>
+        <v>1.37063</v>
       </c>
       <c r="Z10" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="AA10" s="36" t="n">
-        <v>3006520</v>
-      </c>
-      <c r="AB10" s="37" t="n">
-        <v>55.3646140247496</v>
-      </c>
-      <c r="AC10" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD10" s="39" t="n">
-        <v>1.37063</v>
+      <c r="AA10" s="37" t="n">
+        <v>827571</v>
+      </c>
+      <c r="AB10" s="38" t="n">
+        <v>15.2395956098998</v>
+      </c>
+      <c r="AC10" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD10" s="40" t="n">
+        <v>2.86361</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>125</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="6" t="n">
         <v>6963</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="8" t="n">
         <v>66248</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="20" t="n">
         <v>52</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="20" t="n">
         <v>279002</v>
       </c>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="21" t="n">
         <v>4.2114780823572</v>
       </c>
-      <c r="I11" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J11" s="22" t="n">
+      <c r="I11" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" s="23" t="n">
         <v>0.061338</v>
       </c>
-      <c r="K11" s="23" t="n">
+      <c r="K11" s="24" t="n">
         <v>287</v>
       </c>
-      <c r="L11" s="23" t="n">
+      <c r="L11" s="24" t="n">
         <v>247704</v>
       </c>
-      <c r="M11" s="24" t="n">
+      <c r="M11" s="25" t="n">
         <v>3.73904117860162</v>
       </c>
-      <c r="N11" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O11" s="26" t="n">
+      <c r="N11" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O11" s="27" t="n">
         <v>0.140199</v>
       </c>
-      <c r="P11" s="27" t="n">
+      <c r="P11" s="28" t="n">
         <v>89</v>
       </c>
-      <c r="Q11" s="27" t="n">
+      <c r="Q11" s="28" t="n">
         <v>236941</v>
       </c>
-      <c r="R11" s="28" t="n">
+      <c r="R11" s="29" t="n">
         <v>3.57657589663084</v>
       </c>
-      <c r="S11" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T11" s="30" t="n">
+      <c r="S11" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T11" s="31" t="n">
         <v>2.69243</v>
       </c>
-      <c r="U11" s="31" t="n">
+      <c r="U11" s="32" t="n">
         <v>52</v>
       </c>
       <c r="V11" s="32" t="n">
-        <v>195822</v>
+        <v>383168</v>
       </c>
       <c r="W11" s="33" t="n">
-        <v>2.95589300809081</v>
+        <v>5.78384253109528</v>
       </c>
       <c r="X11" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y11" s="35" t="n">
-        <v>0.20884</v>
+        <v>0.123232</v>
       </c>
       <c r="Z11" s="36" t="n">
         <v>52</v>
       </c>
-      <c r="AA11" s="36" t="n">
-        <v>383168</v>
-      </c>
-      <c r="AB11" s="37" t="n">
-        <v>5.78384253109528</v>
-      </c>
-      <c r="AC11" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD11" s="39" t="n">
-        <v>0.123232</v>
+      <c r="AA11" s="37" t="n">
+        <v>195822</v>
+      </c>
+      <c r="AB11" s="38" t="n">
+        <v>2.95589300809081</v>
+      </c>
+      <c r="AC11" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD11" s="40" t="n">
+        <v>0.20884</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="11" t="n">
         <v>1534</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="8" t="n">
         <v>7734</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G12" s="20" t="n">
         <v>10677</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="H12" s="21" t="n">
         <v>1.38052754072925</v>
       </c>
-      <c r="I12" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J12" s="22" t="n">
+      <c r="I12" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" s="23" t="n">
         <v>0.019624</v>
       </c>
-      <c r="K12" s="23" t="n">
+      <c r="K12" s="24" t="n">
         <v>90</v>
       </c>
-      <c r="L12" s="23" t="n">
+      <c r="L12" s="24" t="n">
         <v>10150</v>
       </c>
-      <c r="M12" s="24" t="n">
+      <c r="M12" s="25" t="n">
         <v>1.31238686320145</v>
       </c>
-      <c r="N12" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O12" s="26" t="n">
+      <c r="N12" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O12" s="27" t="n">
         <v>0.044703</v>
       </c>
-      <c r="P12" s="27" t="n">
+      <c r="P12" s="28" t="n">
         <v>18</v>
       </c>
-      <c r="Q12" s="32" t="n">
+      <c r="Q12" s="37" t="n">
         <v>10149</v>
       </c>
-      <c r="R12" s="28" t="n">
+      <c r="R12" s="29" t="n">
         <v>1.3122575640031</v>
       </c>
-      <c r="S12" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T12" s="30" t="n">
+      <c r="S12" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T12" s="31" t="n">
         <v>0.439</v>
       </c>
-      <c r="U12" s="31" t="n">
+      <c r="U12" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="V12" s="31" t="n">
-        <v>12249</v>
+      <c r="V12" s="32" t="n">
+        <v>77034</v>
       </c>
       <c r="W12" s="33" t="n">
-        <v>1.58378588052754</v>
+        <v>9.96043444530644</v>
       </c>
       <c r="X12" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y12" s="35" t="n">
-        <v>0.173475</v>
+        <v>0.086033</v>
       </c>
       <c r="Z12" s="36" t="n">
         <v>15</v>
       </c>
       <c r="AA12" s="36" t="n">
-        <v>77034</v>
-      </c>
-      <c r="AB12" s="37" t="n">
-        <v>9.96043444530644</v>
-      </c>
-      <c r="AC12" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD12" s="39" t="n">
-        <v>0.086033</v>
+        <v>12249</v>
+      </c>
+      <c r="AB12" s="38" t="n">
+        <v>1.58378588052754</v>
+      </c>
+      <c r="AC12" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD12" s="40" t="n">
+        <v>0.173475</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="6" t="n">
         <v>3235</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="8" t="n">
         <v>26389</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="G13" s="19" t="n">
+      <c r="G13" s="20" t="n">
         <v>36326</v>
       </c>
-      <c r="H13" s="20" t="n">
+      <c r="H13" s="21" t="n">
         <v>1.37655841449089</v>
       </c>
-      <c r="I13" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J13" s="22" t="n">
+      <c r="I13" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J13" s="23" t="n">
         <v>0.02987</v>
       </c>
-      <c r="K13" s="23" t="n">
+      <c r="K13" s="24" t="n">
         <v>158</v>
       </c>
-      <c r="L13" s="23" t="n">
+      <c r="L13" s="24" t="n">
         <v>36183</v>
       </c>
-      <c r="M13" s="24" t="n">
+      <c r="M13" s="25" t="n">
         <v>1.37113948993899</v>
       </c>
-      <c r="N13" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O13" s="26" t="n">
+      <c r="N13" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O13" s="27" t="n">
         <v>0.076868</v>
       </c>
-      <c r="P13" s="27" t="n">
+      <c r="P13" s="28" t="n">
         <v>26</v>
       </c>
-      <c r="Q13" s="27" t="n">
+      <c r="Q13" s="28" t="n">
         <v>36163</v>
       </c>
-      <c r="R13" s="28" t="n">
+      <c r="R13" s="29" t="n">
         <v>1.37038159839327</v>
       </c>
-      <c r="S13" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T13" s="30" t="n">
+      <c r="S13" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T13" s="31" t="n">
         <v>0.334391</v>
       </c>
-      <c r="U13" s="31" t="n">
+      <c r="U13" s="32" t="n">
         <v>24</v>
       </c>
       <c r="V13" s="32" t="n">
-        <v>35540</v>
+        <v>162735</v>
       </c>
       <c r="W13" s="33" t="n">
-        <v>1.3467732767441</v>
+        <v>6.16677403463564</v>
       </c>
       <c r="X13" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y13" s="35" t="n">
-        <v>0.982138</v>
+        <v>0.088869</v>
       </c>
       <c r="Z13" s="36" t="n">
         <v>24</v>
       </c>
-      <c r="AA13" s="36" t="n">
-        <v>162735</v>
-      </c>
-      <c r="AB13" s="37" t="n">
-        <v>6.16677403463564</v>
-      </c>
-      <c r="AC13" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD13" s="39" t="n">
-        <v>0.088869</v>
+      <c r="AA13" s="37" t="n">
+        <v>35540</v>
+      </c>
+      <c r="AB13" s="38" t="n">
+        <v>1.3467732767441</v>
+      </c>
+      <c r="AC13" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD13" s="40" t="n">
+        <v>0.982138</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="11" t="n">
         <v>8473</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="8" t="n">
         <v>168200</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="20" t="n">
         <v>84</v>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G14" s="20" t="n">
         <v>304982</v>
       </c>
-      <c r="H14" s="20" t="n">
+      <c r="H14" s="21" t="n">
         <v>1.81321046373365</v>
       </c>
-      <c r="I14" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J14" s="22" t="n">
+      <c r="I14" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J14" s="23" t="n">
         <v>0.059253</v>
       </c>
-      <c r="K14" s="23" t="n">
+      <c r="K14" s="24" t="n">
         <v>429</v>
       </c>
-      <c r="L14" s="32" t="n">
+      <c r="L14" s="37" t="n">
         <v>283848</v>
       </c>
-      <c r="M14" s="24" t="n">
+      <c r="M14" s="25" t="n">
         <v>1.68756242568371</v>
       </c>
-      <c r="N14" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O14" s="26" t="n">
+      <c r="N14" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O14" s="27" t="n">
         <v>0.15874</v>
       </c>
-      <c r="P14" s="27" t="n">
+      <c r="P14" s="28" t="n">
         <v>127</v>
       </c>
-      <c r="Q14" s="32" t="n">
+      <c r="Q14" s="37" t="n">
         <v>283848</v>
       </c>
-      <c r="R14" s="28" t="n">
+      <c r="R14" s="29" t="n">
         <v>1.68756242568371</v>
       </c>
-      <c r="S14" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T14" s="30" t="n">
+      <c r="S14" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T14" s="31" t="n">
         <v>3.4186</v>
       </c>
-      <c r="U14" s="31" t="n">
+      <c r="U14" s="32" t="n">
         <v>84</v>
       </c>
-      <c r="V14" s="31" t="n">
-        <v>357357</v>
+      <c r="V14" s="32" t="n">
+        <v>425773</v>
       </c>
       <c r="W14" s="33" t="n">
-        <v>2.12459571938169</v>
+        <v>2.53134958382878</v>
       </c>
       <c r="X14" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y14" s="35" t="n">
-        <v>0.285767</v>
+        <v>0.132612</v>
       </c>
       <c r="Z14" s="36" t="n">
         <v>84</v>
       </c>
       <c r="AA14" s="36" t="n">
-        <v>425773</v>
-      </c>
-      <c r="AB14" s="37" t="n">
-        <v>2.53134958382878</v>
-      </c>
-      <c r="AC14" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD14" s="39" t="n">
-        <v>0.132612</v>
+        <v>357357</v>
+      </c>
+      <c r="AB14" s="38" t="n">
+        <v>2.12459571938169</v>
+      </c>
+      <c r="AC14" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD14" s="40" t="n">
+        <v>0.285767</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="6" t="n">
         <v>4459</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="E15" s="8" t="n">
         <v>10738</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G15" s="20" t="n">
         <v>14422</v>
       </c>
-      <c r="H15" s="20" t="n">
+      <c r="H15" s="21" t="n">
         <v>1.34308064816539</v>
       </c>
-      <c r="I15" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J15" s="22" t="n">
+      <c r="I15" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J15" s="23" t="n">
         <v>0.05608</v>
       </c>
-      <c r="K15" s="23" t="n">
+      <c r="K15" s="24" t="n">
         <v>103</v>
       </c>
-      <c r="L15" s="23" t="n">
+      <c r="L15" s="24" t="n">
         <v>14422</v>
       </c>
-      <c r="M15" s="24" t="n">
+      <c r="M15" s="25" t="n">
         <v>1.34308064816539</v>
       </c>
-      <c r="N15" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O15" s="26" t="n">
+      <c r="N15" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O15" s="27" t="n">
         <v>0.221851</v>
       </c>
-      <c r="P15" s="27" t="n">
+      <c r="P15" s="28" t="n">
         <v>14</v>
       </c>
-      <c r="Q15" s="27" t="n">
+      <c r="Q15" s="28" t="n">
         <v>14422</v>
       </c>
-      <c r="R15" s="28" t="n">
+      <c r="R15" s="29" t="n">
         <v>1.34308064816539</v>
       </c>
-      <c r="S15" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T15" s="30" t="n">
+      <c r="S15" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T15" s="31" t="n">
         <v>0.894609</v>
       </c>
-      <c r="U15" s="31" t="n">
+      <c r="U15" s="32" t="n">
         <v>14</v>
       </c>
       <c r="V15" s="32" t="n">
-        <v>12482</v>
+        <v>224609</v>
       </c>
       <c r="W15" s="33" t="n">
-        <v>1.16241385732911</v>
+        <v>20.9172099087353</v>
       </c>
       <c r="X15" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y15" s="35" t="n">
-        <v>1.32165</v>
+        <v>1.07643</v>
       </c>
       <c r="Z15" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="AA15" s="36" t="n">
-        <v>224609</v>
-      </c>
-      <c r="AB15" s="37" t="n">
-        <v>20.9172099087353</v>
-      </c>
-      <c r="AC15" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD15" s="39" t="n">
-        <v>1.07643</v>
+      <c r="AA15" s="37" t="n">
+        <v>12482</v>
+      </c>
+      <c r="AB15" s="38" t="n">
+        <v>1.16241385732911</v>
+      </c>
+      <c r="AC15" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD15" s="40" t="n">
+        <v>1.32165</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="11" t="n">
         <v>9139</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="E16" s="8" t="n">
         <v>38350</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="G16" s="19" t="n">
+      <c r="G16" s="20" t="n">
         <v>50942</v>
       </c>
-      <c r="H16" s="20" t="n">
+      <c r="H16" s="21" t="n">
         <v>1.32834419817471</v>
       </c>
-      <c r="I16" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J16" s="22" t="n">
+      <c r="I16" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J16" s="23" t="n">
         <v>0.132169</v>
       </c>
-      <c r="K16" s="23" t="n">
+      <c r="K16" s="24" t="n">
         <v>185</v>
       </c>
-      <c r="L16" s="23" t="n">
+      <c r="L16" s="24" t="n">
         <v>50942</v>
       </c>
-      <c r="M16" s="24" t="n">
+      <c r="M16" s="25" t="n">
         <v>1.32834419817471</v>
       </c>
-      <c r="N16" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O16" s="26" t="n">
+      <c r="N16" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O16" s="27" t="n">
         <v>0.322814</v>
       </c>
-      <c r="P16" s="27" t="n">
+      <c r="P16" s="28" t="n">
         <v>26</v>
       </c>
-      <c r="Q16" s="27" t="n">
+      <c r="Q16" s="28" t="n">
         <v>50942</v>
       </c>
-      <c r="R16" s="28" t="n">
+      <c r="R16" s="29" t="n">
         <v>1.32834419817471</v>
       </c>
-      <c r="S16" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T16" s="30" t="n">
+      <c r="S16" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T16" s="31" t="n">
         <v>0.847419</v>
       </c>
-      <c r="U16" s="31" t="n">
+      <c r="U16" s="32" t="n">
         <v>26</v>
       </c>
       <c r="V16" s="32" t="n">
-        <v>44235</v>
+        <v>460289</v>
       </c>
       <c r="W16" s="33" t="n">
-        <v>1.15345501955671</v>
+        <v>12.0023207301173</v>
       </c>
       <c r="X16" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y16" s="35" t="n">
-        <v>0.780995</v>
+        <v>0.892613</v>
       </c>
       <c r="Z16" s="36" t="n">
         <v>26</v>
       </c>
-      <c r="AA16" s="36" t="n">
-        <v>460289</v>
-      </c>
-      <c r="AB16" s="37" t="n">
-        <v>12.0023207301173</v>
-      </c>
-      <c r="AC16" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD16" s="39" t="n">
-        <v>0.892613</v>
+      <c r="AA16" s="37" t="n">
+        <v>44235</v>
+      </c>
+      <c r="AB16" s="38" t="n">
+        <v>1.15345501955671</v>
+      </c>
+      <c r="AC16" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD16" s="40" t="n">
+        <v>0.780995</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="6" t="n">
         <v>23191</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E17" s="8" t="n">
         <v>205864</v>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F17" s="20" t="n">
         <v>64</v>
       </c>
-      <c r="G17" s="19" t="n">
+      <c r="G17" s="20" t="n">
         <v>292208</v>
       </c>
-      <c r="H17" s="20" t="n">
+      <c r="H17" s="21" t="n">
         <v>1.41942253137994</v>
       </c>
-      <c r="I17" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J17" s="22" t="n">
+      <c r="I17" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J17" s="23" t="n">
         <v>0.216284</v>
       </c>
-      <c r="K17" s="23" t="n">
+      <c r="K17" s="24" t="n">
         <v>436</v>
       </c>
-      <c r="L17" s="23" t="n">
+      <c r="L17" s="24" t="n">
         <v>291985</v>
       </c>
-      <c r="M17" s="24" t="n">
+      <c r="M17" s="25" t="n">
         <v>1.41833929195974</v>
       </c>
-      <c r="N17" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O17" s="26" t="n">
+      <c r="N17" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O17" s="27" t="n">
         <v>0.551641</v>
       </c>
-      <c r="P17" s="27" t="n">
+      <c r="P17" s="28" t="n">
         <v>66</v>
       </c>
-      <c r="Q17" s="27" t="n">
+      <c r="Q17" s="28" t="n">
         <v>291985</v>
       </c>
-      <c r="R17" s="28" t="n">
+      <c r="R17" s="29" t="n">
         <v>1.41833929195974</v>
       </c>
-      <c r="S17" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T17" s="30" t="n">
+      <c r="S17" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T17" s="31" t="n">
         <v>20.6173</v>
       </c>
-      <c r="U17" s="31" t="n">
+      <c r="U17" s="32" t="n">
         <v>64</v>
       </c>
       <c r="V17" s="32" t="n">
-        <v>261662</v>
+        <v>1167940</v>
       </c>
       <c r="W17" s="33" t="n">
-        <v>1.27104301869195</v>
+        <v>5.67335716783896</v>
       </c>
       <c r="X17" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y17" s="35" t="n">
-        <v>13.8255</v>
+        <v>1.31145</v>
       </c>
       <c r="Z17" s="36" t="n">
         <v>64</v>
       </c>
-      <c r="AA17" s="36" t="n">
-        <v>1167940</v>
-      </c>
-      <c r="AB17" s="37" t="n">
-        <v>5.67335716783896</v>
-      </c>
-      <c r="AC17" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD17" s="39" t="n">
-        <v>1.31145</v>
+      <c r="AA17" s="37" t="n">
+        <v>261662</v>
+      </c>
+      <c r="AB17" s="38" t="n">
+        <v>1.27104301869195</v>
+      </c>
+      <c r="AC17" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD17" s="40" t="n">
+        <v>13.8255</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="11" t="n">
         <v>46627</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="E18" s="8" t="n">
         <v>804000</v>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F18" s="20" t="n">
         <v>126</v>
       </c>
-      <c r="G18" s="19" t="n">
+      <c r="G18" s="20" t="n">
         <v>1174240</v>
       </c>
-      <c r="H18" s="20" t="n">
+      <c r="H18" s="21" t="n">
         <v>1.46049751243781</v>
       </c>
-      <c r="I18" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J18" s="22" t="n">
+      <c r="I18" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J18" s="23" t="n">
         <v>0.491527</v>
       </c>
-      <c r="K18" s="23" t="n">
+      <c r="K18" s="24" t="n">
         <v>837</v>
       </c>
-      <c r="L18" s="23" t="n">
+      <c r="L18" s="24" t="n">
         <v>1174090</v>
       </c>
-      <c r="M18" s="24" t="n">
+      <c r="M18" s="25" t="n">
         <v>1.46031094527363</v>
       </c>
-      <c r="N18" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O18" s="26" t="n">
+      <c r="N18" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O18" s="27" t="n">
         <v>1.0065</v>
       </c>
-      <c r="P18" s="27" t="n">
+      <c r="P18" s="28" t="n">
         <v>128</v>
       </c>
-      <c r="Q18" s="27" t="n">
+      <c r="Q18" s="28" t="n">
         <v>1174090</v>
       </c>
-      <c r="R18" s="28" t="n">
+      <c r="R18" s="29" t="n">
         <v>1.46031094527363</v>
       </c>
-      <c r="S18" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T18" s="30" t="n">
+      <c r="S18" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T18" s="31" t="n">
         <v>1.55596</v>
       </c>
-      <c r="U18" s="31" t="n">
+      <c r="U18" s="32" t="n">
         <v>126</v>
       </c>
       <c r="V18" s="32" t="n">
-        <v>1028700</v>
+        <v>2348180</v>
       </c>
       <c r="W18" s="33" t="n">
-        <v>1.2794776119403</v>
+        <v>2.92062189054726</v>
       </c>
       <c r="X18" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y18" s="35" t="n">
-        <v>1.23664</v>
+        <v>1.19038</v>
       </c>
       <c r="Z18" s="36" t="n">
         <v>126</v>
       </c>
-      <c r="AA18" s="36" t="n">
-        <v>2348180</v>
-      </c>
-      <c r="AB18" s="37" t="n">
-        <v>2.92062189054726</v>
-      </c>
-      <c r="AC18" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD18" s="39" t="n">
-        <v>1.19038</v>
+      <c r="AA18" s="37" t="n">
+        <v>1028700</v>
+      </c>
+      <c r="AB18" s="38" t="n">
+        <v>1.2794776119403</v>
+      </c>
+      <c r="AC18" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD18" s="40" t="n">
+        <v>1.23664</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="6" t="n">
         <v>62624</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="E19" s="8" t="n">
         <v>9626</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="20" t="n">
         <v>71</v>
       </c>
-      <c r="G19" s="19" t="n">
+      <c r="G19" s="20" t="n">
         <v>760032</v>
       </c>
-      <c r="H19" s="20" t="n">
+      <c r="H19" s="21" t="n">
         <v>78.9561603989196</v>
       </c>
-      <c r="I19" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J19" s="22" t="n">
+      <c r="I19" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J19" s="23" t="n">
         <v>1.76372</v>
       </c>
-      <c r="K19" s="23" t="n">
+      <c r="K19" s="24" t="n">
         <v>433</v>
       </c>
-      <c r="L19" s="23" t="n">
+      <c r="L19" s="24" t="n">
         <v>686092</v>
       </c>
-      <c r="M19" s="24" t="n">
+      <c r="M19" s="25" t="n">
         <v>71.2748805318928</v>
       </c>
-      <c r="N19" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O19" s="26" t="n">
+      <c r="N19" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O19" s="27" t="n">
         <v>3.87829</v>
       </c>
-      <c r="P19" s="27" t="n">
+      <c r="P19" s="28" t="n">
         <v>274</v>
       </c>
-      <c r="Q19" s="27" t="n">
+      <c r="Q19" s="28" t="n">
         <v>507062</v>
       </c>
-      <c r="R19" s="28" t="n">
+      <c r="R19" s="29" t="n">
         <v>52.6762933721172</v>
       </c>
-      <c r="S19" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T19" s="30" t="n">
+      <c r="S19" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T19" s="31" t="n">
         <v>1748.09</v>
       </c>
-      <c r="U19" s="31" t="n">
+      <c r="U19" s="32" t="n">
         <v>71</v>
       </c>
       <c r="V19" s="32" t="n">
-        <v>421726</v>
+        <v>3154650</v>
       </c>
       <c r="W19" s="33" t="n">
-        <v>43.8111365052982</v>
+        <v>327.721795138168</v>
       </c>
       <c r="X19" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y19" s="35" t="n">
-        <v>4.47966</v>
+        <v>1.63474</v>
       </c>
       <c r="Z19" s="36" t="n">
         <v>71</v>
       </c>
-      <c r="AA19" s="36" t="n">
-        <v>3154650</v>
-      </c>
-      <c r="AB19" s="37" t="n">
-        <v>327.721795138168</v>
-      </c>
-      <c r="AC19" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD19" s="39" t="n">
-        <v>1.63474</v>
+      <c r="AA19" s="37" t="n">
+        <v>421726</v>
+      </c>
+      <c r="AB19" s="38" t="n">
+        <v>43.8111365052982</v>
+      </c>
+      <c r="AC19" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD19" s="40" t="n">
+        <v>4.47966</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="10" t="n">
+      <c r="C20" s="11" t="n">
         <v>1000</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="11" t="n">
         <v>249826</v>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="E20" s="8" t="n">
         <v>12054</v>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F20" s="20" t="n">
         <v>122</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G20" s="20" t="n">
         <v>2695560</v>
       </c>
-      <c r="H20" s="20" t="n">
+      <c r="H20" s="21" t="n">
         <v>223.623693379791</v>
       </c>
-      <c r="I20" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J20" s="22" t="n">
+      <c r="I20" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J20" s="23" t="n">
         <v>6.34666</v>
       </c>
-      <c r="K20" s="23" t="n">
+      <c r="K20" s="24" t="n">
         <v>754</v>
       </c>
-      <c r="L20" s="23" t="n">
+      <c r="L20" s="24" t="n">
         <v>2487940</v>
       </c>
-      <c r="M20" s="24" t="n">
+      <c r="M20" s="25" t="n">
         <v>206.399535423926</v>
       </c>
-      <c r="N20" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O20" s="26" t="n">
+      <c r="N20" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O20" s="27" t="n">
         <v>24.9574</v>
       </c>
-      <c r="P20" s="27" t="n">
+      <c r="P20" s="28" t="n">
         <v>275</v>
       </c>
-      <c r="Q20" s="27"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="29" t="s">
+      <c r="Q20" s="28"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="T20" s="30" t="n">
+      <c r="T20" s="31" t="n">
         <v>72000</v>
       </c>
-      <c r="U20" s="31" t="n">
+      <c r="U20" s="32" t="n">
         <v>122</v>
       </c>
       <c r="V20" s="32" t="n">
-        <v>1299170</v>
+        <v>12552200</v>
       </c>
       <c r="W20" s="33" t="n">
-        <v>107.779160444666</v>
+        <v>1041.33067861291</v>
       </c>
       <c r="X20" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y20" s="35" t="n">
-        <v>37.3919</v>
+        <v>7.93733</v>
       </c>
       <c r="Z20" s="36" t="n">
         <v>122</v>
       </c>
-      <c r="AA20" s="36" t="n">
-        <v>12552200</v>
-      </c>
-      <c r="AB20" s="37" t="n">
-        <v>1041.33067861291</v>
-      </c>
-      <c r="AC20" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD20" s="39" t="n">
-        <v>7.93733</v>
+      <c r="AA20" s="37" t="n">
+        <v>1299170</v>
+      </c>
+      <c r="AB20" s="38" t="n">
+        <v>107.779160444666</v>
+      </c>
+      <c r="AC20" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD20" s="40" t="n">
+        <v>37.3919</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" s="6" t="n">
         <v>17910</v>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="E21" s="8" t="n">
         <v>94362</v>
       </c>
-      <c r="F21" s="19" t="n">
+      <c r="F21" s="20" t="n">
         <v>63</v>
       </c>
-      <c r="G21" s="19" t="n">
+      <c r="G21" s="20" t="n">
         <v>441099</v>
       </c>
-      <c r="H21" s="20" t="n">
+      <c r="H21" s="21" t="n">
         <v>4.67454059896993</v>
       </c>
-      <c r="I21" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J21" s="22" t="n">
+      <c r="I21" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J21" s="23" t="n">
         <v>0.146082</v>
       </c>
-      <c r="K21" s="23" t="n">
+      <c r="K21" s="24" t="n">
         <v>401</v>
       </c>
-      <c r="L21" s="23" t="n">
+      <c r="L21" s="24" t="n">
         <v>400501</v>
       </c>
-      <c r="M21" s="24" t="n">
+      <c r="M21" s="25" t="n">
         <v>4.24430385112651</v>
       </c>
-      <c r="N21" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O21" s="26" t="n">
+      <c r="N21" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O21" s="27" t="n">
         <v>0.414933</v>
       </c>
-      <c r="P21" s="27" t="n">
+      <c r="P21" s="28" t="n">
         <v>95</v>
       </c>
-      <c r="Q21" s="27" t="n">
+      <c r="Q21" s="28" t="n">
         <v>373731</v>
       </c>
-      <c r="R21" s="28" t="n">
+      <c r="R21" s="29" t="n">
         <v>3.96060914351116</v>
       </c>
-      <c r="S21" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T21" s="30" t="n">
+      <c r="S21" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T21" s="31" t="n">
         <v>4.01552</v>
       </c>
-      <c r="U21" s="31" t="n">
+      <c r="U21" s="32" t="n">
         <v>63</v>
       </c>
       <c r="V21" s="32" t="n">
-        <v>323096</v>
+        <v>900025</v>
       </c>
       <c r="W21" s="33" t="n">
-        <v>3.42400542591297</v>
+        <v>9.53800258578665</v>
       </c>
       <c r="X21" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y21" s="35" t="n">
-        <v>0.711709</v>
+        <v>0.346675</v>
       </c>
       <c r="Z21" s="36" t="n">
         <v>63</v>
       </c>
-      <c r="AA21" s="36" t="n">
-        <v>900025</v>
-      </c>
-      <c r="AB21" s="37" t="n">
-        <v>9.53800258578665</v>
-      </c>
-      <c r="AC21" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD21" s="39" t="n">
-        <v>0.346675</v>
+      <c r="AA21" s="37" t="n">
+        <v>323096</v>
+      </c>
+      <c r="AB21" s="38" t="n">
+        <v>3.42400542591297</v>
+      </c>
+      <c r="AC21" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD21" s="40" t="n">
+        <v>0.711709</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C22" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="11" t="n">
         <v>17910</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E22" s="8" t="n">
         <v>150839</v>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="20" t="n">
         <v>77</v>
       </c>
-      <c r="G22" s="19" t="n">
+      <c r="G22" s="20" t="n">
         <v>590043</v>
       </c>
-      <c r="H22" s="20" t="n">
+      <c r="H22" s="21" t="n">
         <v>3.9117403324074</v>
       </c>
-      <c r="I22" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J22" s="22" t="n">
+      <c r="I22" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J22" s="23" t="n">
         <v>0.154598</v>
       </c>
-      <c r="K22" s="23" t="n">
+      <c r="K22" s="24" t="n">
         <v>437</v>
       </c>
-      <c r="L22" s="23" t="n">
+      <c r="L22" s="24" t="n">
         <v>508452</v>
       </c>
-      <c r="M22" s="24" t="n">
+      <c r="M22" s="25" t="n">
         <v>3.37082584742673</v>
       </c>
-      <c r="N22" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O22" s="26" t="n">
+      <c r="N22" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O22" s="27" t="n">
         <v>0.425751</v>
       </c>
-      <c r="P22" s="27" t="n">
+      <c r="P22" s="28" t="n">
         <v>150</v>
       </c>
-      <c r="Q22" s="32" t="n">
+      <c r="Q22" s="37" t="n">
         <v>449471</v>
       </c>
-      <c r="R22" s="28" t="n">
+      <c r="R22" s="29" t="n">
         <v>2.97980628352084</v>
       </c>
-      <c r="S22" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T22" s="30" t="n">
+      <c r="S22" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T22" s="31" t="n">
         <v>8.55077</v>
       </c>
-      <c r="U22" s="31" t="n">
+      <c r="U22" s="32" t="n">
         <v>77</v>
       </c>
-      <c r="V22" s="31" t="n">
-        <v>462439</v>
+      <c r="V22" s="32" t="n">
+        <v>902235</v>
       </c>
       <c r="W22" s="33" t="n">
-        <v>3.06577874422397</v>
+        <v>5.98144379106199</v>
       </c>
       <c r="X22" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y22" s="35" t="n">
-        <v>0.902978</v>
+        <v>0.351181</v>
       </c>
       <c r="Z22" s="36" t="n">
         <v>77</v>
       </c>
       <c r="AA22" s="36" t="n">
-        <v>902235</v>
-      </c>
-      <c r="AB22" s="37" t="n">
-        <v>5.98144379106199</v>
-      </c>
-      <c r="AC22" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD22" s="39" t="n">
-        <v>0.351181</v>
+        <v>462439</v>
+      </c>
+      <c r="AB22" s="38" t="n">
+        <v>3.06577874422397</v>
+      </c>
+      <c r="AC22" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD22" s="40" t="n">
+        <v>0.902978</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="6" t="n">
         <v>64</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D23" s="6" t="n">
         <v>1824</v>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="E23" s="8" t="n">
         <v>32736</v>
       </c>
-      <c r="F23" s="19" t="n">
+      <c r="F23" s="20" t="n">
         <v>32</v>
       </c>
-      <c r="G23" s="19" t="n">
+      <c r="G23" s="20" t="n">
         <v>60192</v>
       </c>
-      <c r="H23" s="20" t="n">
+      <c r="H23" s="21" t="n">
         <v>1.83870967741936</v>
       </c>
-      <c r="I23" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J23" s="22" t="n">
+      <c r="I23" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J23" s="23" t="n">
         <v>0.012723</v>
       </c>
-      <c r="K23" s="23" t="n">
+      <c r="K23" s="24" t="n">
         <v>143</v>
       </c>
-      <c r="L23" s="23" t="n">
+      <c r="L23" s="24" t="n">
         <v>60192</v>
       </c>
-      <c r="M23" s="24" t="n">
+      <c r="M23" s="25" t="n">
         <v>1.83870967741936</v>
       </c>
-      <c r="N23" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O23" s="26" t="n">
+      <c r="N23" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O23" s="27" t="n">
         <v>0.029021</v>
       </c>
-      <c r="P23" s="27" t="n">
+      <c r="P23" s="28" t="n">
         <v>32</v>
       </c>
-      <c r="Q23" s="27" t="n">
+      <c r="Q23" s="28" t="n">
         <v>60192</v>
       </c>
-      <c r="R23" s="28" t="n">
+      <c r="R23" s="29" t="n">
         <v>1.83870967741936</v>
       </c>
-      <c r="S23" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T23" s="30" t="n">
+      <c r="S23" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T23" s="31" t="n">
         <v>0.10753</v>
       </c>
-      <c r="U23" s="31" t="n">
+      <c r="U23" s="32" t="n">
         <v>32</v>
       </c>
       <c r="V23" s="32" t="n">
-        <v>32735</v>
+        <v>60192</v>
       </c>
       <c r="W23" s="33" t="n">
-        <v>0.99996945259042</v>
+        <v>1.83870967741936</v>
       </c>
       <c r="X23" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y23" s="35" t="n">
-        <v>0.734866</v>
+        <v>0.026735</v>
       </c>
       <c r="Z23" s="36" t="n">
         <v>32</v>
       </c>
-      <c r="AA23" s="36" t="n">
-        <v>60192</v>
-      </c>
-      <c r="AB23" s="37" t="n">
-        <v>1.83870967741936</v>
-      </c>
-      <c r="AC23" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD23" s="39" t="n">
-        <v>0.026735</v>
+      <c r="AA23" s="37" t="n">
+        <v>32735</v>
+      </c>
+      <c r="AB23" s="38" t="n">
+        <v>0.99996945259042</v>
+      </c>
+      <c r="AC23" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD23" s="40" t="n">
+        <v>0.734866</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C24" s="11" t="n">
         <v>64</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="11" t="n">
         <v>704</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="E24" s="8" t="n">
         <v>396</v>
       </c>
-      <c r="F24" s="19" t="n">
+      <c r="F24" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="G24" s="19" t="n">
+      <c r="G24" s="20" t="n">
         <v>4264</v>
       </c>
-      <c r="H24" s="20" t="n">
+      <c r="H24" s="21" t="n">
         <v>10.7676767676768</v>
       </c>
-      <c r="I24" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J24" s="22" t="n">
+      <c r="I24" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J24" s="23" t="n">
         <v>0.007656</v>
       </c>
-      <c r="K24" s="23" t="n">
+      <c r="K24" s="24" t="n">
         <v>53</v>
       </c>
-      <c r="L24" s="23" t="n">
+      <c r="L24" s="24" t="n">
         <v>3917</v>
       </c>
-      <c r="M24" s="24" t="n">
+      <c r="M24" s="25" t="n">
         <v>9.89141414141414</v>
       </c>
-      <c r="N24" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O24" s="26" t="n">
+      <c r="N24" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O24" s="27" t="n">
         <v>0.017102</v>
       </c>
-      <c r="P24" s="27" t="n">
+      <c r="P24" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="Q24" s="27" t="n">
+      <c r="Q24" s="28" t="n">
         <v>3872</v>
       </c>
-      <c r="R24" s="28" t="n">
+      <c r="R24" s="29" t="n">
         <v>9.77777777777778</v>
       </c>
-      <c r="S24" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T24" s="30" t="n">
+      <c r="S24" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T24" s="31" t="n">
         <v>0.302912</v>
       </c>
-      <c r="U24" s="31" t="n">
+      <c r="U24" s="32" t="n">
         <v>7</v>
       </c>
       <c r="V24" s="32" t="n">
-        <v>2058</v>
+        <v>23232</v>
       </c>
       <c r="W24" s="33" t="n">
-        <v>5.1969696969697</v>
+        <v>58.6666666666667</v>
       </c>
       <c r="X24" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y24" s="35" t="n">
-        <v>0.071017</v>
+        <v>0.016441</v>
       </c>
       <c r="Z24" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="AA24" s="36" t="n">
-        <v>23232</v>
-      </c>
-      <c r="AB24" s="37" t="n">
-        <v>58.6666666666667</v>
-      </c>
-      <c r="AC24" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD24" s="39" t="n">
-        <v>0.016441</v>
+      <c r="AA24" s="37" t="n">
+        <v>2058</v>
+      </c>
+      <c r="AB24" s="38" t="n">
+        <v>5.1969696969697</v>
+      </c>
+      <c r="AC24" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD24" s="40" t="n">
+        <v>0.071017</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="6" t="n">
         <v>256</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D25" s="6" t="n">
         <v>31616</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E25" s="8" t="n">
         <v>800624</v>
       </c>
-      <c r="F25" s="19" t="n">
+      <c r="F25" s="20" t="n">
         <v>130</v>
       </c>
-      <c r="G25" s="19" t="n">
+      <c r="G25" s="20" t="n">
         <v>1558810</v>
       </c>
-      <c r="H25" s="20" t="n">
+      <c r="H25" s="21" t="n">
         <v>1.94699384480106</v>
       </c>
-      <c r="I25" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J25" s="22" t="n">
+      <c r="I25" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J25" s="23" t="n">
         <v>0.26085</v>
       </c>
-      <c r="K25" s="23" t="n">
+      <c r="K25" s="24" t="n">
         <v>613</v>
       </c>
-      <c r="L25" s="23" t="n">
+      <c r="L25" s="24" t="n">
         <v>1558460</v>
       </c>
-      <c r="M25" s="24" t="n">
+      <c r="M25" s="25" t="n">
         <v>1.94655668578509</v>
       </c>
-      <c r="N25" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O25" s="26" t="n">
+      <c r="N25" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O25" s="27" t="n">
         <v>0.554622</v>
       </c>
-      <c r="P25" s="27" t="n">
+      <c r="P25" s="28" t="n">
         <v>134</v>
       </c>
-      <c r="Q25" s="27" t="n">
+      <c r="Q25" s="28" t="n">
         <v>1558460</v>
       </c>
-      <c r="R25" s="28" t="n">
+      <c r="R25" s="29" t="n">
         <v>1.94655668578509</v>
       </c>
-      <c r="S25" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T25" s="30" t="n">
+      <c r="S25" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T25" s="31" t="n">
         <v>0.631232</v>
       </c>
-      <c r="U25" s="31" t="n">
+      <c r="U25" s="32" t="n">
         <v>130</v>
       </c>
       <c r="V25" s="32" t="n">
-        <v>1115000</v>
+        <v>1558460</v>
       </c>
       <c r="W25" s="33" t="n">
-        <v>1.39266372229661</v>
+        <v>1.94655668578509</v>
       </c>
       <c r="X25" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y25" s="35" t="n">
-        <v>1.3935</v>
+        <v>0.593759</v>
       </c>
       <c r="Z25" s="36" t="n">
         <v>130</v>
       </c>
-      <c r="AA25" s="36" t="n">
-        <v>1558460</v>
-      </c>
-      <c r="AB25" s="37" t="n">
-        <v>1.94655668578509</v>
-      </c>
-      <c r="AC25" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD25" s="39" t="n">
-        <v>0.593759</v>
+      <c r="AA25" s="37" t="n">
+        <v>1115000</v>
+      </c>
+      <c r="AB25" s="38" t="n">
+        <v>1.39266372229661</v>
+      </c>
+      <c r="AC25" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD25" s="40" t="n">
+        <v>1.3935</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="10" t="n">
+      <c r="C26" s="11" t="n">
         <v>256</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="11" t="n">
         <v>20864</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E26" s="8" t="n">
         <v>12360</v>
       </c>
-      <c r="F26" s="19" t="n">
+      <c r="F26" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="G26" s="19" t="n">
+      <c r="G26" s="20" t="n">
         <v>146767</v>
       </c>
-      <c r="H26" s="20" t="n">
+      <c r="H26" s="21" t="n">
         <v>11.8743527508091</v>
       </c>
-      <c r="I26" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J26" s="22" t="n">
+      <c r="I26" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J26" s="23" t="n">
         <v>0.261491</v>
       </c>
-      <c r="K26" s="23" t="n">
+      <c r="K26" s="24" t="n">
         <v>172</v>
       </c>
-      <c r="L26" s="23" t="n">
+      <c r="L26" s="24" t="n">
         <v>128691</v>
       </c>
-      <c r="M26" s="24" t="n">
+      <c r="M26" s="25" t="n">
         <v>10.4118932038835</v>
       </c>
-      <c r="N26" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O26" s="26" t="n">
+      <c r="N26" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O26" s="27" t="n">
         <v>0.593104</v>
       </c>
-      <c r="P26" s="27" t="n">
+      <c r="P26" s="28" t="n">
         <v>39</v>
       </c>
-      <c r="Q26" s="27" t="n">
+      <c r="Q26" s="28" t="n">
         <v>127632</v>
       </c>
-      <c r="R26" s="28" t="n">
+      <c r="R26" s="29" t="n">
         <v>10.326213592233</v>
       </c>
-      <c r="S26" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T26" s="30" t="n">
+      <c r="S26" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T26" s="31" t="n">
         <v>2.44162</v>
       </c>
-      <c r="U26" s="31" t="n">
+      <c r="U26" s="32" t="n">
         <v>24</v>
       </c>
       <c r="V26" s="32" t="n">
-        <v>51082</v>
+        <v>1021060</v>
       </c>
       <c r="W26" s="33" t="n">
-        <v>4.13284789644013</v>
+        <v>82.6100323624596</v>
       </c>
       <c r="X26" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y26" s="35" t="n">
-        <v>1.79225</v>
+        <v>0.45931</v>
       </c>
       <c r="Z26" s="36" t="n">
         <v>24</v>
       </c>
-      <c r="AA26" s="36" t="n">
-        <v>1021060</v>
-      </c>
-      <c r="AB26" s="37" t="n">
-        <v>82.6100323624596</v>
-      </c>
-      <c r="AC26" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD26" s="39" t="n">
-        <v>0.45931</v>
+      <c r="AA26" s="37" t="n">
+        <v>51082</v>
+      </c>
+      <c r="AB26" s="38" t="n">
+        <v>4.13284789644013</v>
+      </c>
+      <c r="AC26" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD26" s="40" t="n">
+        <v>1.79225</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D27" s="6" t="n">
         <v>210</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="E27" s="8" t="n">
         <v>192</v>
       </c>
-      <c r="F27" s="19" t="n">
+      <c r="F27" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="G27" s="19" t="n">
+      <c r="G27" s="20" t="n">
         <v>1079</v>
       </c>
-      <c r="H27" s="20" t="n">
+      <c r="H27" s="21" t="n">
         <v>5.61979166666667</v>
       </c>
-      <c r="I27" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J27" s="22" t="n">
+      <c r="I27" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J27" s="23" t="n">
         <v>0.003218</v>
       </c>
-      <c r="K27" s="23" t="n">
+      <c r="K27" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="L27" s="23" t="n">
+      <c r="L27" s="24" t="n">
         <v>900</v>
       </c>
-      <c r="M27" s="24" t="n">
+      <c r="M27" s="25" t="n">
         <v>4.6875</v>
       </c>
-      <c r="N27" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O27" s="26" t="n">
+      <c r="N27" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O27" s="27" t="n">
         <v>0.005102</v>
       </c>
-      <c r="P27" s="27" t="n">
+      <c r="P27" s="28" t="n">
         <v>12</v>
       </c>
-      <c r="Q27" s="27" t="n">
+      <c r="Q27" s="28" t="n">
         <v>900</v>
       </c>
-      <c r="R27" s="28" t="n">
+      <c r="R27" s="29" t="n">
         <v>4.6875</v>
       </c>
-      <c r="S27" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T27" s="30" t="n">
+      <c r="S27" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T27" s="31" t="n">
         <v>0.315263</v>
       </c>
-      <c r="U27" s="31" t="n">
+      <c r="U27" s="32" t="n">
         <v>6</v>
       </c>
       <c r="V27" s="32" t="n">
-        <v>659</v>
+        <v>3150</v>
       </c>
       <c r="W27" s="33" t="n">
-        <v>3.43229166666667</v>
+        <v>16.40625</v>
       </c>
       <c r="X27" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y27" s="35" t="n">
-        <v>0.007589</v>
+        <v>0.004874</v>
       </c>
       <c r="Z27" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="AA27" s="36" t="n">
-        <v>3150</v>
-      </c>
-      <c r="AB27" s="37" t="n">
-        <v>16.40625</v>
-      </c>
-      <c r="AC27" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD27" s="39" t="n">
-        <v>0.004874</v>
+      <c r="AA27" s="37" t="n">
+        <v>659</v>
+      </c>
+      <c r="AB27" s="38" t="n">
+        <v>3.43229166666667</v>
+      </c>
+      <c r="AC27" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD27" s="40" t="n">
+        <v>0.007589</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C28" s="11" t="n">
         <v>70</v>
       </c>
-      <c r="D28" s="10" t="n">
+      <c r="D28" s="11" t="n">
         <v>1855</v>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="E28" s="8" t="n">
         <v>6552</v>
       </c>
-      <c r="F28" s="19" t="n">
+      <c r="F28" s="20" t="n">
         <v>19</v>
       </c>
-      <c r="G28" s="19" t="n">
+      <c r="G28" s="20" t="n">
         <v>29569</v>
       </c>
-      <c r="H28" s="20" t="n">
+      <c r="H28" s="21" t="n">
         <v>4.51297313797314</v>
       </c>
-      <c r="I28" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J28" s="22" t="n">
+      <c r="I28" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J28" s="23" t="n">
         <v>0.017795</v>
       </c>
-      <c r="K28" s="23" t="n">
+      <c r="K28" s="24" t="n">
         <v>111</v>
       </c>
-      <c r="L28" s="23" t="n">
+      <c r="L28" s="24" t="n">
         <v>26712</v>
       </c>
-      <c r="M28" s="24" t="n">
+      <c r="M28" s="25" t="n">
         <v>4.07692307692308</v>
       </c>
-      <c r="N28" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O28" s="26" t="n">
+      <c r="N28" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O28" s="27" t="n">
         <v>0.033205</v>
       </c>
-      <c r="P28" s="27" t="n">
+      <c r="P28" s="28" t="n">
         <v>30</v>
       </c>
-      <c r="Q28" s="27" t="n">
+      <c r="Q28" s="28" t="n">
         <v>26711</v>
       </c>
-      <c r="R28" s="28" t="n">
+      <c r="R28" s="29" t="n">
         <v>4.07677045177045</v>
       </c>
-      <c r="S28" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T28" s="30" t="n">
+      <c r="S28" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T28" s="31" t="n">
         <v>0.560329</v>
       </c>
-      <c r="U28" s="31" t="n">
+      <c r="U28" s="32" t="n">
         <v>19</v>
       </c>
       <c r="V28" s="32" t="n">
-        <v>17783</v>
+        <v>66780</v>
       </c>
       <c r="W28" s="33" t="n">
-        <v>2.71413308913309</v>
+        <v>10.1923076923077</v>
       </c>
       <c r="X28" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y28" s="35" t="n">
-        <v>0.739449</v>
+        <v>0.031561</v>
       </c>
       <c r="Z28" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="AA28" s="36" t="n">
-        <v>66780</v>
-      </c>
-      <c r="AB28" s="37" t="n">
-        <v>10.1923076923077</v>
-      </c>
-      <c r="AC28" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD28" s="39" t="n">
-        <v>0.031561</v>
+      <c r="AA28" s="37" t="n">
+        <v>17783</v>
+      </c>
+      <c r="AB28" s="38" t="n">
+        <v>2.71413308913309</v>
+      </c>
+      <c r="AC28" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD28" s="40" t="n">
+        <v>0.739449</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="6" t="n">
         <v>120</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D29" s="6" t="n">
         <v>5460</v>
       </c>
-      <c r="E29" s="7" t="n">
+      <c r="E29" s="8" t="n">
         <v>3808</v>
       </c>
-      <c r="F29" s="19" t="n">
+      <c r="F29" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="G29" s="19" t="n">
+      <c r="G29" s="20" t="n">
         <v>51783</v>
       </c>
-      <c r="H29" s="20" t="n">
+      <c r="H29" s="21" t="n">
         <v>13.5984768907563</v>
       </c>
-      <c r="I29" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J29" s="22" t="n">
+      <c r="I29" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J29" s="23" t="n">
         <v>0.063807</v>
       </c>
-      <c r="K29" s="23" t="n">
+      <c r="K29" s="24" t="n">
         <v>91</v>
       </c>
-      <c r="L29" s="23" t="n">
+      <c r="L29" s="24" t="n">
         <v>42805</v>
       </c>
-      <c r="M29" s="24" t="n">
+      <c r="M29" s="25" t="n">
         <v>11.2408088235294</v>
       </c>
-      <c r="N29" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O29" s="26" t="n">
+      <c r="N29" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O29" s="27" t="n">
         <v>0.117954</v>
       </c>
-      <c r="P29" s="27" t="n">
+      <c r="P29" s="28" t="n">
         <v>29</v>
       </c>
-      <c r="Q29" s="27" t="n">
+      <c r="Q29" s="28" t="n">
         <v>41181</v>
       </c>
-      <c r="R29" s="28" t="n">
+      <c r="R29" s="29" t="n">
         <v>10.8143382352941</v>
       </c>
-      <c r="S29" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T29" s="30" t="n">
+      <c r="S29" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T29" s="31" t="n">
         <v>0.91388</v>
       </c>
-      <c r="U29" s="31" t="n">
+      <c r="U29" s="32" t="n">
         <v>15</v>
       </c>
       <c r="V29" s="32" t="n">
-        <v>19740</v>
+        <v>308860</v>
       </c>
       <c r="W29" s="33" t="n">
-        <v>5.18382352941176</v>
+        <v>81.1081932773109</v>
       </c>
       <c r="X29" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y29" s="35" t="n">
-        <v>0.216525</v>
+        <v>0.095813</v>
       </c>
       <c r="Z29" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="AA29" s="36" t="n">
-        <v>308860</v>
-      </c>
-      <c r="AB29" s="37" t="n">
-        <v>81.1081932773109</v>
-      </c>
-      <c r="AC29" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD29" s="39" t="n">
-        <v>0.095813</v>
+      <c r="AA29" s="37" t="n">
+        <v>19740</v>
+      </c>
+      <c r="AB29" s="38" t="n">
+        <v>5.18382352941176</v>
+      </c>
+      <c r="AC29" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD29" s="40" t="n">
+        <v>0.216525</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="10" t="n">
+      <c r="C30" s="11" t="n">
         <v>171</v>
       </c>
-      <c r="D30" s="10" t="n">
+      <c r="D30" s="11" t="n">
         <v>9435</v>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E30" s="8" t="n">
         <v>6745</v>
       </c>
-      <c r="F30" s="19" t="n">
+      <c r="F30" s="20" t="n">
         <v>33</v>
       </c>
-      <c r="G30" s="19" t="n">
+      <c r="G30" s="20" t="n">
         <v>143426</v>
       </c>
-      <c r="H30" s="20" t="n">
+      <c r="H30" s="21" t="n">
         <v>21.26404744255</v>
       </c>
-      <c r="I30" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J30" s="22" t="n">
+      <c r="I30" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J30" s="23" t="n">
         <v>0.099043</v>
       </c>
-      <c r="K30" s="23" t="n">
+      <c r="K30" s="24" t="n">
         <v>162</v>
       </c>
-      <c r="L30" s="23" t="n">
+      <c r="L30" s="24" t="n">
         <v>82197</v>
       </c>
-      <c r="M30" s="24" t="n">
+      <c r="M30" s="25" t="n">
         <v>12.1863602668643</v>
       </c>
-      <c r="N30" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O30" s="26" t="n">
+      <c r="N30" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O30" s="27" t="n">
         <v>0.268401</v>
       </c>
-      <c r="P30" s="27" t="n">
+      <c r="P30" s="28" t="n">
         <v>77</v>
       </c>
-      <c r="Q30" s="32" t="n">
+      <c r="Q30" s="37" t="n">
         <v>70425</v>
       </c>
-      <c r="R30" s="28" t="n">
+      <c r="R30" s="29" t="n">
         <v>10.4410674573758</v>
       </c>
-      <c r="S30" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T30" s="30" t="n">
+      <c r="S30" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T30" s="31" t="n">
         <v>4.34797</v>
       </c>
-      <c r="U30" s="31" t="n">
+      <c r="U30" s="32" t="n">
         <v>33</v>
       </c>
-      <c r="V30" s="31" t="n">
-        <v>89874</v>
+      <c r="V30" s="32" t="n">
+        <v>483595</v>
       </c>
       <c r="W30" s="33" t="n">
-        <v>13.3245366938473</v>
+        <v>71.6968124536694</v>
       </c>
       <c r="X30" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y30" s="35" t="n">
-        <v>0.485566</v>
+        <v>0.18763</v>
       </c>
       <c r="Z30" s="36" t="n">
         <v>33</v>
       </c>
       <c r="AA30" s="36" t="n">
-        <v>483595</v>
-      </c>
-      <c r="AB30" s="37" t="n">
-        <v>71.6968124536694</v>
-      </c>
-      <c r="AC30" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD30" s="39" t="n">
-        <v>0.18763</v>
+        <v>89874</v>
+      </c>
+      <c r="AB30" s="38" t="n">
+        <v>13.3245366938473</v>
+      </c>
+      <c r="AC30" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD30" s="40" t="n">
+        <v>0.485566</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="D31" s="6" t="n">
         <v>918</v>
       </c>
-      <c r="E31" s="7" t="n">
+      <c r="E31" s="8" t="n">
         <v>5460</v>
       </c>
-      <c r="F31" s="19" t="n">
+      <c r="F31" s="20" t="n">
         <v>21</v>
       </c>
-      <c r="G31" s="19" t="n">
+      <c r="G31" s="20" t="n">
         <v>15019</v>
       </c>
-      <c r="H31" s="20" t="n">
+      <c r="H31" s="21" t="n">
         <v>2.7507326007326</v>
       </c>
-      <c r="I31" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J31" s="22" t="n">
+      <c r="I31" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J31" s="23" t="n">
         <v>0.008653</v>
       </c>
-      <c r="K31" s="23" t="n">
+      <c r="K31" s="24" t="n">
         <v>63</v>
       </c>
-      <c r="L31" s="23" t="n">
+      <c r="L31" s="24" t="n">
         <v>14568</v>
       </c>
-      <c r="M31" s="24" t="n">
+      <c r="M31" s="25" t="n">
         <v>2.66813186813187</v>
       </c>
-      <c r="N31" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O31" s="26" t="n">
+      <c r="N31" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O31" s="27" t="n">
         <v>0.016654</v>
       </c>
-      <c r="P31" s="27" t="n">
+      <c r="P31" s="28" t="n">
         <v>30</v>
       </c>
-      <c r="Q31" s="27" t="n">
+      <c r="Q31" s="28" t="n">
         <v>14568</v>
       </c>
-      <c r="R31" s="28" t="n">
+      <c r="R31" s="29" t="n">
         <v>2.66813186813187</v>
       </c>
-      <c r="S31" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T31" s="30" t="n">
+      <c r="S31" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T31" s="31" t="n">
         <v>0.450179</v>
       </c>
-      <c r="U31" s="31" t="n">
+      <c r="U31" s="32" t="n">
         <v>21</v>
       </c>
       <c r="V31" s="32" t="n">
-        <v>10500</v>
+        <v>21654</v>
       </c>
       <c r="W31" s="33" t="n">
-        <v>1.92307692307692</v>
+        <v>3.96593406593407</v>
       </c>
       <c r="X31" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y31" s="35" t="n">
-        <v>0.322022</v>
+        <v>0.015353</v>
       </c>
       <c r="Z31" s="36" t="n">
         <v>21</v>
       </c>
-      <c r="AA31" s="36" t="n">
-        <v>21654</v>
-      </c>
-      <c r="AB31" s="37" t="n">
-        <v>3.96593406593407</v>
-      </c>
-      <c r="AC31" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD31" s="39" t="n">
-        <v>0.015353</v>
+      <c r="AA31" s="37" t="n">
+        <v>10500</v>
+      </c>
+      <c r="AB31" s="38" t="n">
+        <v>1.92307692307692</v>
+      </c>
+      <c r="AC31" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD31" s="40" t="n">
+        <v>0.322022</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="10" t="n">
+      <c r="C32" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="D32" s="10" t="n">
+      <c r="D32" s="11" t="n">
         <v>10933</v>
       </c>
-      <c r="E32" s="7" t="n">
+      <c r="E32" s="8" t="n">
         <v>3321</v>
       </c>
-      <c r="F32" s="19" t="n">
+      <c r="F32" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="G32" s="19" t="n">
+      <c r="G32" s="20" t="n">
         <v>77256</v>
       </c>
-      <c r="H32" s="20" t="n">
+      <c r="H32" s="21" t="n">
         <v>23.2628726287263</v>
       </c>
-      <c r="I32" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J32" s="22" t="n">
+      <c r="I32" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J32" s="23" t="n">
         <v>0.171954</v>
       </c>
-      <c r="K32" s="23" t="n">
+      <c r="K32" s="24" t="n">
         <v>163</v>
       </c>
-      <c r="L32" s="23" t="n">
+      <c r="L32" s="24" t="n">
         <v>72028</v>
       </c>
-      <c r="M32" s="24" t="n">
+      <c r="M32" s="25" t="n">
         <v>21.6886479975911</v>
       </c>
-      <c r="N32" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O32" s="26" t="n">
+      <c r="N32" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O32" s="27" t="n">
         <v>0.467208</v>
       </c>
-      <c r="P32" s="27" t="n">
+      <c r="P32" s="28" t="n">
         <v>436</v>
       </c>
-      <c r="Q32" s="27" t="n">
+      <c r="Q32" s="28" t="n">
         <v>47398</v>
       </c>
-      <c r="R32" s="28" t="n">
+      <c r="R32" s="29" t="n">
         <v>14.2722071665161</v>
       </c>
-      <c r="S32" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T32" s="30" t="n">
+      <c r="S32" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T32" s="31" t="n">
         <v>8818.2</v>
       </c>
-      <c r="U32" s="31" t="n">
+      <c r="U32" s="32" t="n">
         <v>24</v>
       </c>
       <c r="V32" s="32" t="n">
-        <v>45326</v>
+        <v>548977</v>
       </c>
       <c r="W32" s="33" t="n">
-        <v>13.6482987052093</v>
+        <v>165.304727491719</v>
       </c>
       <c r="X32" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y32" s="35" t="n">
-        <v>6.12396</v>
+        <v>0.426277</v>
       </c>
       <c r="Z32" s="36" t="n">
         <v>24</v>
       </c>
-      <c r="AA32" s="36" t="n">
-        <v>548977</v>
-      </c>
-      <c r="AB32" s="37" t="n">
-        <v>165.304727491719</v>
-      </c>
-      <c r="AC32" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD32" s="39" t="n">
-        <v>0.426277</v>
+      <c r="AA32" s="37" t="n">
+        <v>45326</v>
+      </c>
+      <c r="AB32" s="38" t="n">
+        <v>13.6482987052093</v>
+      </c>
+      <c r="AC32" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD32" s="40" t="n">
+        <v>6.12396</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="D33" s="5" t="n">
+      <c r="D33" s="6" t="n">
         <v>21928</v>
       </c>
-      <c r="E33" s="7" t="n">
+      <c r="E33" s="8" t="n">
         <v>31564</v>
       </c>
-      <c r="F33" s="19" t="n">
+      <c r="F33" s="20" t="n">
         <v>46</v>
       </c>
-      <c r="G33" s="19" t="n">
+      <c r="G33" s="20" t="n">
         <v>291593</v>
       </c>
-      <c r="H33" s="20" t="n">
+      <c r="H33" s="21" t="n">
         <v>9.23815105816753</v>
       </c>
-      <c r="I33" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J33" s="22" t="n">
+      <c r="I33" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J33" s="23" t="n">
         <v>0.323929</v>
       </c>
-      <c r="K33" s="23" t="n">
+      <c r="K33" s="24" t="n">
         <v>327</v>
       </c>
-      <c r="L33" s="23" t="n">
+      <c r="L33" s="24" t="n">
         <v>267307</v>
       </c>
-      <c r="M33" s="24" t="n">
+      <c r="M33" s="25" t="n">
         <v>8.46873019896084</v>
       </c>
-      <c r="N33" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O33" s="26" t="n">
+      <c r="N33" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O33" s="27" t="n">
         <v>0.894598</v>
       </c>
-      <c r="P33" s="27" t="n">
+      <c r="P33" s="28" t="n">
         <v>426</v>
       </c>
-      <c r="Q33" s="27" t="n">
+      <c r="Q33" s="28" t="n">
         <v>189356</v>
       </c>
-      <c r="R33" s="28" t="n">
+      <c r="R33" s="29" t="n">
         <v>5.9991129134457</v>
       </c>
-      <c r="S33" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T33" s="30" t="n">
+      <c r="S33" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T33" s="31" t="n">
         <v>140.226</v>
       </c>
-      <c r="U33" s="31" t="n">
+      <c r="U33" s="32" t="n">
         <v>46</v>
       </c>
       <c r="V33" s="32" t="n">
-        <v>170564</v>
+        <v>1104340</v>
       </c>
       <c r="W33" s="33" t="n">
-        <v>5.40375110885819</v>
+        <v>34.9873273349385</v>
       </c>
       <c r="X33" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y33" s="35" t="n">
-        <v>2.90848</v>
+        <v>0.599245</v>
       </c>
       <c r="Z33" s="36" t="n">
         <v>46</v>
       </c>
-      <c r="AA33" s="36" t="n">
-        <v>1104340</v>
-      </c>
-      <c r="AB33" s="37" t="n">
-        <v>34.9873273349385</v>
-      </c>
-      <c r="AC33" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD33" s="39" t="n">
-        <v>0.599245</v>
+      <c r="AA33" s="37" t="n">
+        <v>170564</v>
+      </c>
+      <c r="AB33" s="38" t="n">
+        <v>5.40375110885819</v>
+      </c>
+      <c r="AC33" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD33" s="40" t="n">
+        <v>2.90848</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C34" s="10" t="n">
+      <c r="C34" s="11" t="n">
         <v>300</v>
       </c>
-      <c r="D34" s="10" t="n">
+      <c r="D34" s="11" t="n">
         <v>33390</v>
       </c>
-      <c r="E34" s="7" t="n">
+      <c r="E34" s="8" t="n">
         <v>63390</v>
       </c>
-      <c r="F34" s="19" t="n">
+      <c r="F34" s="20" t="n">
         <v>72</v>
       </c>
-      <c r="G34" s="19" t="n">
+      <c r="G34" s="20" t="n">
         <v>719292</v>
       </c>
-      <c r="H34" s="20" t="n">
+      <c r="H34" s="21" t="n">
         <v>11.3470894462849</v>
       </c>
-      <c r="I34" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J34" s="22" t="n">
+      <c r="I34" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J34" s="23" t="n">
         <v>0.62658</v>
       </c>
-      <c r="K34" s="23" t="n">
+      <c r="K34" s="24" t="n">
         <v>490</v>
       </c>
-      <c r="L34" s="23" t="n">
+      <c r="L34" s="24" t="n">
         <v>632613</v>
       </c>
-      <c r="M34" s="24" t="n">
+      <c r="M34" s="25" t="n">
         <v>9.97969711310932</v>
       </c>
-      <c r="N34" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O34" s="26" t="n">
+      <c r="N34" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O34" s="27" t="n">
         <v>1.24673</v>
       </c>
-      <c r="P34" s="27" t="n">
+      <c r="P34" s="28" t="n">
         <v>317</v>
       </c>
-      <c r="Q34" s="27" t="n">
+      <c r="Q34" s="28" t="n">
         <v>499285</v>
       </c>
-      <c r="R34" s="28" t="n">
+      <c r="R34" s="29" t="n">
         <v>7.87640006310144</v>
       </c>
-      <c r="S34" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T34" s="30" t="n">
+      <c r="S34" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T34" s="31" t="n">
         <v>68.3747</v>
       </c>
-      <c r="U34" s="31" t="n">
+      <c r="U34" s="32" t="n">
         <v>72</v>
       </c>
       <c r="V34" s="32" t="n">
-        <v>417722</v>
+        <v>1681600</v>
       </c>
       <c r="W34" s="33" t="n">
-        <v>6.5897144660041</v>
+        <v>26.5278435084398</v>
       </c>
       <c r="X34" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y34" s="35" t="n">
-        <v>1.99112</v>
+        <v>0.716147</v>
       </c>
       <c r="Z34" s="36" t="n">
         <v>72</v>
       </c>
-      <c r="AA34" s="36" t="n">
-        <v>1681600</v>
-      </c>
-      <c r="AB34" s="37" t="n">
-        <v>26.5278435084398</v>
-      </c>
-      <c r="AC34" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD34" s="39" t="n">
-        <v>0.716147</v>
+      <c r="AA34" s="37" t="n">
+        <v>417722</v>
+      </c>
+      <c r="AB34" s="38" t="n">
+        <v>6.5897144660041</v>
+      </c>
+      <c r="AC34" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD34" s="40" t="n">
+        <v>1.99112</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="D35" s="5" t="n">
+      <c r="D35" s="6" t="n">
         <v>31569</v>
       </c>
-      <c r="E35" s="7" t="n">
+      <c r="E35" s="8" t="n">
         <v>4764</v>
       </c>
-      <c r="F35" s="19" t="n">
+      <c r="F35" s="20" t="n">
         <v>36</v>
       </c>
-      <c r="G35" s="19" t="n">
+      <c r="G35" s="20" t="n">
         <v>200341</v>
       </c>
-      <c r="H35" s="20" t="n">
+      <c r="H35" s="21" t="n">
         <v>42.0531066330814</v>
       </c>
-      <c r="I35" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J35" s="22" t="n">
+      <c r="I35" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J35" s="23" t="n">
         <v>0.622325</v>
       </c>
-      <c r="K35" s="23" t="n">
+      <c r="K35" s="24" t="n">
         <v>244</v>
       </c>
-      <c r="L35" s="23" t="n">
+      <c r="L35" s="24" t="n">
         <v>188291</v>
       </c>
-      <c r="M35" s="24" t="n">
+      <c r="M35" s="25" t="n">
         <v>39.5237195633921</v>
       </c>
-      <c r="N35" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O35" s="26" t="n">
+      <c r="N35" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O35" s="27" t="n">
         <v>1.63508</v>
       </c>
-      <c r="P35" s="27" t="n">
+      <c r="P35" s="28" t="n">
         <v>183</v>
       </c>
-      <c r="Q35" s="27"/>
-      <c r="R35" s="28"/>
-      <c r="S35" s="29" t="s">
+      <c r="Q35" s="28"/>
+      <c r="R35" s="29"/>
+      <c r="S35" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="T35" s="30" t="n">
+      <c r="T35" s="31" t="n">
         <v>72000</v>
       </c>
-      <c r="U35" s="31" t="n">
+      <c r="U35" s="32" t="n">
         <v>36</v>
       </c>
       <c r="V35" s="32" t="n">
-        <v>106787</v>
+        <v>1594430</v>
       </c>
       <c r="W35" s="33" t="n">
-        <v>22.4154072208228</v>
+        <v>334.683039462636</v>
       </c>
       <c r="X35" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y35" s="35" t="n">
-        <v>9.59384</v>
+        <v>1.44128</v>
       </c>
       <c r="Z35" s="36" t="n">
         <v>36</v>
       </c>
-      <c r="AA35" s="36" t="n">
-        <v>1594430</v>
-      </c>
-      <c r="AB35" s="37" t="n">
-        <v>334.683039462636</v>
-      </c>
-      <c r="AC35" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD35" s="39" t="n">
-        <v>1.44128</v>
+      <c r="AA35" s="37" t="n">
+        <v>106787</v>
+      </c>
+      <c r="AB35" s="38" t="n">
+        <v>22.4154072208228</v>
+      </c>
+      <c r="AC35" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD35" s="40" t="n">
+        <v>9.59384</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="10" t="n">
+      <c r="C36" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="D36" s="10" t="n">
+      <c r="D36" s="11" t="n">
         <v>62946</v>
       </c>
-      <c r="E36" s="7" t="n">
+      <c r="E36" s="8" t="n">
         <v>63870</v>
       </c>
-      <c r="F36" s="19" t="n">
+      <c r="F36" s="20" t="n">
         <v>69</v>
       </c>
-      <c r="G36" s="19" t="n">
+      <c r="G36" s="20" t="n">
         <v>797997</v>
       </c>
-      <c r="H36" s="20" t="n">
+      <c r="H36" s="21" t="n">
         <v>12.494081728511</v>
       </c>
-      <c r="I36" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J36" s="22" t="n">
+      <c r="I36" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J36" s="23" t="n">
         <v>1.21941</v>
       </c>
-      <c r="K36" s="23" t="n">
+      <c r="K36" s="24" t="n">
         <v>497</v>
       </c>
-      <c r="L36" s="23" t="n">
+      <c r="L36" s="24" t="n">
         <v>727405</v>
       </c>
-      <c r="M36" s="24" t="n">
+      <c r="M36" s="25" t="n">
         <v>11.388836699546</v>
       </c>
-      <c r="N36" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O36" s="26" t="n">
+      <c r="N36" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O36" s="27" t="n">
         <v>3.52028</v>
       </c>
-      <c r="P36" s="27" t="n">
+      <c r="P36" s="28" t="n">
         <v>751</v>
       </c>
-      <c r="Q36" s="27" t="n">
+      <c r="Q36" s="28" t="n">
         <v>496848</v>
       </c>
-      <c r="R36" s="28" t="n">
+      <c r="R36" s="29" t="n">
         <v>7.77905119774542</v>
       </c>
-      <c r="S36" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T36" s="30" t="n">
+      <c r="S36" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T36" s="31" t="n">
         <v>1659.92</v>
       </c>
-      <c r="U36" s="31" t="n">
+      <c r="U36" s="32" t="n">
         <v>69</v>
       </c>
       <c r="V36" s="32" t="n">
-        <v>398085</v>
+        <v>3169750</v>
       </c>
       <c r="W36" s="33" t="n">
-        <v>6.23273837482386</v>
+        <v>49.6281509315798</v>
       </c>
       <c r="X36" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y36" s="35" t="n">
-        <v>4.67435</v>
+        <v>1.94401</v>
       </c>
       <c r="Z36" s="36" t="n">
         <v>69</v>
       </c>
-      <c r="AA36" s="36" t="n">
-        <v>3169750</v>
-      </c>
-      <c r="AB36" s="37" t="n">
-        <v>49.6281509315798</v>
-      </c>
-      <c r="AC36" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD36" s="39" t="n">
-        <v>1.94401</v>
+      <c r="AA36" s="37" t="n">
+        <v>398085</v>
+      </c>
+      <c r="AB36" s="38" t="n">
+        <v>6.23273837482386</v>
+      </c>
+      <c r="AC36" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD36" s="40" t="n">
+        <v>4.67435</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C37" s="6" t="n">
         <v>700</v>
       </c>
-      <c r="D37" s="5" t="n">
+      <c r="D37" s="6" t="n">
         <v>60999</v>
       </c>
-      <c r="E37" s="7" t="n">
+      <c r="E37" s="8" t="n">
         <v>5185</v>
       </c>
-      <c r="F37" s="19" t="n">
+      <c r="F37" s="20" t="n">
         <v>44</v>
       </c>
-      <c r="G37" s="19" t="n">
+      <c r="G37" s="20" t="n">
         <v>344530</v>
       </c>
-      <c r="H37" s="20" t="n">
+      <c r="H37" s="21" t="n">
         <v>66.4474445515911</v>
       </c>
-      <c r="I37" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J37" s="22" t="n">
+      <c r="I37" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J37" s="23" t="n">
         <v>1.37617</v>
       </c>
-      <c r="K37" s="23" t="n">
+      <c r="K37" s="24" t="n">
         <v>306</v>
       </c>
-      <c r="L37" s="23" t="n">
+      <c r="L37" s="24" t="n">
         <v>329451</v>
       </c>
-      <c r="M37" s="24" t="n">
+      <c r="M37" s="25" t="n">
         <v>63.5392478302797</v>
       </c>
-      <c r="N37" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O37" s="26" t="n">
+      <c r="N37" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O37" s="27" t="n">
         <v>3.66368</v>
       </c>
-      <c r="P37" s="27" t="n">
+      <c r="P37" s="28" t="n">
         <v>89</v>
       </c>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="29" t="s">
+      <c r="Q37" s="28"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="T37" s="30" t="n">
+      <c r="T37" s="31" t="n">
         <v>72000</v>
       </c>
-      <c r="U37" s="31" t="n">
+      <c r="U37" s="32" t="n">
         <v>44</v>
       </c>
       <c r="V37" s="32" t="n">
-        <v>163455</v>
+        <v>3068790</v>
       </c>
       <c r="W37" s="33" t="n">
-        <v>31.5245901639344</v>
+        <v>591.859209257474</v>
       </c>
       <c r="X37" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y37" s="35" t="n">
-        <v>10.3878</v>
+        <v>3.35107</v>
       </c>
       <c r="Z37" s="36" t="n">
         <v>44</v>
       </c>
-      <c r="AA37" s="36" t="n">
-        <v>3068790</v>
-      </c>
-      <c r="AB37" s="37" t="n">
-        <v>591.859209257474</v>
-      </c>
-      <c r="AC37" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD37" s="39" t="n">
-        <v>3.35107</v>
+      <c r="AA37" s="37" t="n">
+        <v>163455</v>
+      </c>
+      <c r="AB37" s="38" t="n">
+        <v>31.5245901639344</v>
+      </c>
+      <c r="AC37" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD37" s="40" t="n">
+        <v>10.3878</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C38" s="10" t="n">
+      <c r="C38" s="11" t="n">
         <v>1000</v>
       </c>
-      <c r="D38" s="10" t="n">
+      <c r="D38" s="11" t="n">
         <v>122253</v>
       </c>
-      <c r="E38" s="7" t="n">
+      <c r="E38" s="8" t="n">
         <v>5436</v>
       </c>
-      <c r="F38" s="19" t="n">
+      <c r="F38" s="20" t="n">
         <v>56</v>
       </c>
-      <c r="G38" s="19" t="n">
+      <c r="G38" s="20" t="n">
         <v>637294</v>
       </c>
-      <c r="H38" s="20" t="n">
+      <c r="H38" s="21" t="n">
         <v>117.235835172921</v>
       </c>
-      <c r="I38" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J38" s="22" t="n">
+      <c r="I38" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J38" s="23" t="n">
         <v>3.76834</v>
       </c>
-      <c r="K38" s="23" t="n">
+      <c r="K38" s="24" t="n">
         <v>394</v>
       </c>
-      <c r="L38" s="23" t="n">
+      <c r="L38" s="24" t="n">
         <v>606734</v>
       </c>
-      <c r="M38" s="24" t="n">
+      <c r="M38" s="25" t="n">
         <v>111.614054451803</v>
       </c>
-      <c r="N38" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O38" s="26" t="n">
+      <c r="N38" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O38" s="27" t="n">
         <v>9.13231</v>
       </c>
-      <c r="P38" s="27" t="n">
+      <c r="P38" s="28" t="n">
         <v>56</v>
       </c>
-      <c r="Q38" s="27"/>
-      <c r="R38" s="28"/>
-      <c r="S38" s="29" t="s">
+      <c r="Q38" s="28"/>
+      <c r="R38" s="29"/>
+      <c r="S38" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="T38" s="30" t="n">
+      <c r="T38" s="31" t="n">
         <v>72000</v>
       </c>
-      <c r="U38" s="31" t="n">
+      <c r="U38" s="32" t="n">
         <v>56</v>
       </c>
       <c r="V38" s="32" t="n">
-        <v>269810</v>
+        <v>6149880</v>
       </c>
       <c r="W38" s="33" t="n">
-        <v>49.6339220014717</v>
+        <v>1131.32450331126</v>
       </c>
       <c r="X38" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y38" s="35" t="n">
-        <v>23.5913</v>
+        <v>8.72503</v>
       </c>
       <c r="Z38" s="36" t="n">
         <v>56</v>
       </c>
-      <c r="AA38" s="36" t="n">
-        <v>6149880</v>
-      </c>
-      <c r="AB38" s="37" t="n">
-        <v>1131.32450331126</v>
-      </c>
-      <c r="AC38" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD38" s="39" t="n">
-        <v>8.72503</v>
+      <c r="AA38" s="37" t="n">
+        <v>269810</v>
+      </c>
+      <c r="AB38" s="38" t="n">
+        <v>49.6339220014717</v>
+      </c>
+      <c r="AC38" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD38" s="40" t="n">
+        <v>23.5913</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C39" s="6" t="n">
         <v>1500</v>
       </c>
-      <c r="D39" s="5" t="n">
+      <c r="D39" s="6" t="n">
         <v>284923</v>
       </c>
-      <c r="E39" s="7" t="n">
+      <c r="E39" s="8" t="n">
         <v>7135</v>
       </c>
-      <c r="F39" s="19" t="n">
-        <v>78</v>
-      </c>
-      <c r="G39" s="19" t="n">
+      <c r="F39" s="20" t="n">
+        <v>78</v>
+      </c>
+      <c r="G39" s="20" t="n">
         <v>1377910</v>
       </c>
-      <c r="H39" s="20" t="n">
+      <c r="H39" s="21" t="n">
         <v>193.119831814997</v>
       </c>
-      <c r="I39" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J39" s="22" t="n">
+      <c r="I39" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J39" s="23" t="n">
         <v>11.1905</v>
       </c>
-      <c r="K39" s="23" t="n">
+      <c r="K39" s="24" t="n">
         <v>558</v>
       </c>
-      <c r="L39" s="23" t="n">
+      <c r="L39" s="24" t="n">
         <v>1329570</v>
       </c>
-      <c r="M39" s="24" t="n">
+      <c r="M39" s="25" t="n">
         <v>186.344779257183</v>
       </c>
-      <c r="N39" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O39" s="26" t="n">
+      <c r="N39" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O39" s="27" t="n">
         <v>29.2251</v>
       </c>
-      <c r="P39" s="27" t="n">
-        <v>78</v>
-      </c>
-      <c r="Q39" s="27"/>
-      <c r="R39" s="28"/>
-      <c r="S39" s="29" t="s">
+      <c r="P39" s="28" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="29"/>
+      <c r="S39" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="T39" s="30" t="n">
+      <c r="T39" s="31" t="n">
         <v>72000</v>
       </c>
-      <c r="U39" s="31" t="n">
+      <c r="U39" s="32" t="n">
         <v>78</v>
       </c>
       <c r="V39" s="32" t="n">
+        <v>14314400</v>
+      </c>
+      <c r="W39" s="33" t="n">
+        <v>2006.22284512964</v>
+      </c>
+      <c r="X39" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y39" s="35" t="n">
+        <v>29.9334</v>
+      </c>
+      <c r="Z39" s="36" t="n">
+        <v>78</v>
+      </c>
+      <c r="AA39" s="37" t="n">
         <v>533596</v>
       </c>
-      <c r="W39" s="33" t="n">
+      <c r="AB39" s="38" t="n">
         <v>74.7857042747022</v>
       </c>
-      <c r="X39" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y39" s="35" t="n">
+      <c r="AC39" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD39" s="40" t="n">
         <v>67.4759</v>
       </c>
-      <c r="Z39" s="36" t="n">
-        <v>78</v>
-      </c>
-      <c r="AA39" s="36" t="n">
-        <v>14314400</v>
-      </c>
-      <c r="AB39" s="37" t="n">
-        <v>2006.22284512964</v>
-      </c>
-      <c r="AC39" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD39" s="39" t="n">
-        <v>29.9334</v>
-      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="10" t="n">
+      <c r="C40" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D40" s="10" t="n">
+      <c r="D40" s="11" t="n">
         <v>13930</v>
       </c>
-      <c r="E40" s="7" t="n">
+      <c r="E40" s="8" t="n">
         <v>45295</v>
       </c>
-      <c r="F40" s="19" t="n">
+      <c r="F40" s="20" t="n">
         <v>31</v>
       </c>
-      <c r="G40" s="19" t="n">
+      <c r="G40" s="20" t="n">
         <v>191976</v>
       </c>
-      <c r="H40" s="20" t="n">
+      <c r="H40" s="21" t="n">
         <v>4.23834860359863</v>
       </c>
-      <c r="I40" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J40" s="22" t="n">
+      <c r="I40" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J40" s="23" t="n">
         <v>0.117169</v>
       </c>
-      <c r="K40" s="23" t="n">
+      <c r="K40" s="24" t="n">
         <v>266</v>
       </c>
-      <c r="L40" s="23" t="n">
+      <c r="L40" s="24" t="n">
         <v>187149</v>
       </c>
-      <c r="M40" s="24" t="n">
+      <c r="M40" s="25" t="n">
         <v>4.13178054972955</v>
       </c>
-      <c r="N40" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O40" s="26" t="n">
+      <c r="N40" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O40" s="27" t="n">
         <v>0.415434</v>
       </c>
-      <c r="P40" s="27" t="n">
+      <c r="P40" s="28" t="n">
         <v>63</v>
       </c>
-      <c r="Q40" s="27" t="n">
+      <c r="Q40" s="28" t="n">
         <v>174760</v>
       </c>
-      <c r="R40" s="28" t="n">
+      <c r="R40" s="29" t="n">
         <v>3.85826250137984</v>
       </c>
-      <c r="S40" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T40" s="30" t="n">
+      <c r="S40" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T40" s="31" t="n">
         <v>3.91908</v>
       </c>
-      <c r="U40" s="31" t="n">
+      <c r="U40" s="32" t="n">
         <v>31</v>
       </c>
       <c r="V40" s="32" t="n">
-        <v>82936</v>
+        <v>701610</v>
       </c>
       <c r="W40" s="33" t="n">
-        <v>1.83101887625566</v>
+        <v>15.4897891599514</v>
       </c>
       <c r="X40" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y40" s="35" t="n">
-        <v>0.50822</v>
+        <v>0.278</v>
       </c>
       <c r="Z40" s="36" t="n">
         <v>31</v>
       </c>
-      <c r="AA40" s="36" t="n">
-        <v>701610</v>
-      </c>
-      <c r="AB40" s="37" t="n">
-        <v>15.4897891599514</v>
-      </c>
-      <c r="AC40" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD40" s="39" t="n">
-        <v>0.278</v>
+      <c r="AA40" s="37" t="n">
+        <v>82936</v>
+      </c>
+      <c r="AB40" s="38" t="n">
+        <v>1.83101887625566</v>
+      </c>
+      <c r="AC40" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD40" s="40" t="n">
+        <v>0.50822</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C41" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D41" s="5" t="n">
+      <c r="D41" s="6" t="n">
         <v>13930</v>
       </c>
-      <c r="E41" s="7" t="n">
+      <c r="E41" s="8" t="n">
         <v>15073</v>
       </c>
-      <c r="F41" s="19" t="n">
+      <c r="F41" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="G41" s="19" t="n">
+      <c r="G41" s="20" t="n">
         <v>122916</v>
       </c>
-      <c r="H41" s="20" t="n">
+      <c r="H41" s="21" t="n">
         <v>8.15471372653088</v>
       </c>
-      <c r="I41" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J41" s="22" t="n">
+      <c r="I41" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J41" s="23" t="n">
         <v>0.127644</v>
       </c>
-      <c r="K41" s="23" t="n">
+      <c r="K41" s="24" t="n">
         <v>183</v>
       </c>
-      <c r="L41" s="23" t="n">
+      <c r="L41" s="24" t="n">
         <v>122916</v>
       </c>
-      <c r="M41" s="24" t="n">
+      <c r="M41" s="25" t="n">
         <v>8.15471372653088</v>
       </c>
-      <c r="N41" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O41" s="26" t="n">
+      <c r="N41" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O41" s="27" t="n">
         <v>0.338138</v>
       </c>
-      <c r="P41" s="27" t="n">
+      <c r="P41" s="28" t="n">
         <v>22</v>
       </c>
-      <c r="Q41" s="27" t="n">
+      <c r="Q41" s="28" t="n">
         <v>122024</v>
       </c>
-      <c r="R41" s="28" t="n">
+      <c r="R41" s="29" t="n">
         <v>8.09553506269489</v>
       </c>
-      <c r="S41" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T41" s="30" t="n">
+      <c r="S41" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T41" s="31" t="n">
         <v>0.535249</v>
       </c>
-      <c r="U41" s="31" t="n">
+      <c r="U41" s="32" t="n">
         <v>18</v>
       </c>
       <c r="V41" s="32" t="n">
-        <v>28693</v>
+        <v>701018</v>
       </c>
       <c r="W41" s="33" t="n">
-        <v>1.90360246798912</v>
+        <v>46.508193458502</v>
       </c>
       <c r="X41" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y41" s="35" t="n">
-        <v>0.576967</v>
+        <v>0.290948</v>
       </c>
       <c r="Z41" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="AA41" s="36" t="n">
-        <v>701018</v>
-      </c>
-      <c r="AB41" s="37" t="n">
-        <v>46.508193458502</v>
-      </c>
-      <c r="AC41" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD41" s="39" t="n">
-        <v>0.290948</v>
+      <c r="AA41" s="37" t="n">
+        <v>28693</v>
+      </c>
+      <c r="AB41" s="38" t="n">
+        <v>1.90360246798912</v>
+      </c>
+      <c r="AC41" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD41" s="40" t="n">
+        <v>0.576967</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="10" t="n">
+      <c r="C42" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D42" s="10" t="n">
+      <c r="D42" s="11" t="n">
         <v>17910</v>
       </c>
-      <c r="E42" s="7" t="n">
+      <c r="E42" s="8" t="n">
         <v>242710</v>
       </c>
-      <c r="F42" s="19" t="n">
+      <c r="F42" s="20" t="n">
         <v>74</v>
       </c>
-      <c r="G42" s="19" t="n">
+      <c r="G42" s="20" t="n">
         <v>582448</v>
       </c>
-      <c r="H42" s="20" t="n">
+      <c r="H42" s="21" t="n">
         <v>2.39976927197067</v>
       </c>
-      <c r="I42" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J42" s="22" t="n">
+      <c r="I42" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J42" s="23" t="n">
         <v>0.158252</v>
       </c>
-      <c r="K42" s="23" t="n">
+      <c r="K42" s="24" t="n">
         <v>446</v>
       </c>
-      <c r="L42" s="23" t="n">
+      <c r="L42" s="24" t="n">
         <v>543024</v>
       </c>
-      <c r="M42" s="24" t="n">
+      <c r="M42" s="25" t="n">
         <v>2.23733673931853</v>
       </c>
-      <c r="N42" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O42" s="26" t="n">
+      <c r="N42" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O42" s="27" t="n">
         <v>0.423835</v>
       </c>
-      <c r="P42" s="27" t="n">
+      <c r="P42" s="28" t="n">
         <v>116</v>
       </c>
-      <c r="Q42" s="27" t="n">
+      <c r="Q42" s="28" t="n">
         <v>525646</v>
       </c>
-      <c r="R42" s="28" t="n">
+      <c r="R42" s="29" t="n">
         <v>2.16573688764369</v>
       </c>
-      <c r="S42" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T42" s="30" t="n">
+      <c r="S42" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T42" s="31" t="n">
         <v>5.59613</v>
       </c>
-      <c r="U42" s="31" t="n">
+      <c r="U42" s="32" t="n">
         <v>74</v>
       </c>
       <c r="V42" s="32" t="n">
-        <v>430841</v>
+        <v>900586</v>
       </c>
       <c r="W42" s="33" t="n">
-        <v>1.77512669440897</v>
+        <v>3.71054344691195</v>
       </c>
       <c r="X42" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y42" s="35" t="n">
-        <v>0.644852</v>
+        <v>0.345597</v>
       </c>
       <c r="Z42" s="36" t="n">
         <v>74</v>
       </c>
-      <c r="AA42" s="36" t="n">
-        <v>900586</v>
-      </c>
-      <c r="AB42" s="37" t="n">
-        <v>3.71054344691195</v>
-      </c>
-      <c r="AC42" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD42" s="39" t="n">
-        <v>0.345597</v>
+      <c r="AA42" s="37" t="n">
+        <v>430841</v>
+      </c>
+      <c r="AB42" s="38" t="n">
+        <v>1.77512669440897</v>
+      </c>
+      <c r="AC42" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD42" s="40" t="n">
+        <v>0.644852</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C43" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D43" s="5" t="n">
+      <c r="D43" s="6" t="n">
         <v>17910</v>
       </c>
-      <c r="E43" s="7" t="n">
+      <c r="E43" s="8" t="n">
         <v>178468</v>
       </c>
-      <c r="F43" s="19" t="n">
+      <c r="F43" s="20" t="n">
         <v>75</v>
       </c>
-      <c r="G43" s="19" t="n">
+      <c r="G43" s="20" t="n">
         <v>578346</v>
       </c>
-      <c r="H43" s="20" t="n">
+      <c r="H43" s="21" t="n">
         <v>3.24061456395544</v>
       </c>
-      <c r="I43" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J43" s="22" t="n">
+      <c r="I43" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J43" s="23" t="n">
         <v>0.152855</v>
       </c>
-      <c r="K43" s="23" t="n">
+      <c r="K43" s="24" t="n">
         <v>437</v>
       </c>
-      <c r="L43" s="23" t="n">
+      <c r="L43" s="24" t="n">
         <v>516205</v>
       </c>
-      <c r="M43" s="24" t="n">
+      <c r="M43" s="25" t="n">
         <v>2.89242329157048</v>
       </c>
-      <c r="N43" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O43" s="26" t="n">
+      <c r="N43" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O43" s="27" t="n">
         <v>0.394185</v>
       </c>
-      <c r="P43" s="27" t="n">
+      <c r="P43" s="28" t="n">
         <v>152</v>
       </c>
-      <c r="Q43" s="27" t="n">
+      <c r="Q43" s="28" t="n">
         <v>465232</v>
       </c>
-      <c r="R43" s="28" t="n">
+      <c r="R43" s="29" t="n">
         <v>2.60680906380976</v>
       </c>
-      <c r="S43" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T43" s="30" t="n">
+      <c r="S43" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T43" s="31" t="n">
         <v>9.3982</v>
       </c>
-      <c r="U43" s="31" t="n">
+      <c r="U43" s="32" t="n">
         <v>75</v>
       </c>
       <c r="V43" s="32" t="n">
-        <v>440813</v>
+        <v>900484</v>
       </c>
       <c r="W43" s="33" t="n">
-        <v>2.46998341439362</v>
+        <v>5.04563283053545</v>
       </c>
       <c r="X43" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y43" s="35" t="n">
-        <v>0.732179</v>
+        <v>0.333274</v>
       </c>
       <c r="Z43" s="36" t="n">
         <v>75</v>
       </c>
-      <c r="AA43" s="36" t="n">
-        <v>900484</v>
-      </c>
-      <c r="AB43" s="37" t="n">
-        <v>5.04563283053545</v>
-      </c>
-      <c r="AC43" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD43" s="39" t="n">
-        <v>0.333274</v>
+      <c r="AA43" s="37" t="n">
+        <v>440813</v>
+      </c>
+      <c r="AB43" s="38" t="n">
+        <v>2.46998341439362</v>
+      </c>
+      <c r="AC43" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD43" s="40" t="n">
+        <v>0.732179</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C44" s="10" t="n">
+      <c r="C44" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="11" t="n">
         <v>17910</v>
       </c>
-      <c r="E44" s="7" t="n">
+      <c r="E44" s="8" t="n">
         <v>96764</v>
       </c>
-      <c r="F44" s="19" t="n">
+      <c r="F44" s="20" t="n">
         <v>56</v>
       </c>
-      <c r="G44" s="19" t="n">
+      <c r="G44" s="20" t="n">
         <v>430170</v>
       </c>
-      <c r="H44" s="20" t="n">
+      <c r="H44" s="21" t="n">
         <v>4.44555826547063</v>
       </c>
-      <c r="I44" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J44" s="22" t="n">
+      <c r="I44" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J44" s="23" t="n">
         <v>0.150179</v>
       </c>
-      <c r="K44" s="23" t="n">
+      <c r="K44" s="24" t="n">
         <v>408</v>
       </c>
-      <c r="L44" s="23" t="n">
+      <c r="L44" s="24" t="n">
         <v>397231</v>
       </c>
-      <c r="M44" s="24" t="n">
+      <c r="M44" s="25" t="n">
         <v>4.10515274275557</v>
       </c>
-      <c r="N44" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O44" s="26" t="n">
+      <c r="N44" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O44" s="27" t="n">
         <v>0.419642</v>
       </c>
-      <c r="P44" s="27" t="n">
+      <c r="P44" s="28" t="n">
         <v>82</v>
       </c>
-      <c r="Q44" s="27" t="n">
+      <c r="Q44" s="28" t="n">
         <v>373572</v>
       </c>
-      <c r="R44" s="28" t="n">
+      <c r="R44" s="29" t="n">
         <v>3.86065065520235</v>
       </c>
-      <c r="S44" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T44" s="30" t="n">
+      <c r="S44" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T44" s="31" t="n">
         <v>2.79931</v>
       </c>
-      <c r="U44" s="31" t="n">
+      <c r="U44" s="32" t="n">
         <v>56</v>
       </c>
       <c r="V44" s="32" t="n">
-        <v>261071</v>
+        <v>900152</v>
       </c>
       <c r="W44" s="33" t="n">
-        <v>2.69801785788103</v>
+        <v>9.30255053532305</v>
       </c>
       <c r="X44" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y44" s="35" t="n">
-        <v>0.772128</v>
+        <v>0.325985</v>
       </c>
       <c r="Z44" s="36" t="n">
         <v>56</v>
       </c>
-      <c r="AA44" s="36" t="n">
-        <v>900152</v>
-      </c>
-      <c r="AB44" s="37" t="n">
-        <v>9.30255053532305</v>
-      </c>
-      <c r="AC44" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD44" s="39" t="n">
-        <v>0.325985</v>
+      <c r="AA44" s="37" t="n">
+        <v>261071</v>
+      </c>
+      <c r="AB44" s="38" t="n">
+        <v>2.69801785788103</v>
+      </c>
+      <c r="AC44" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD44" s="40" t="n">
+        <v>0.772128</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C45" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="D45" s="5" t="n">
+      <c r="D45" s="6" t="n">
         <v>39900</v>
       </c>
-      <c r="E45" s="7" t="n">
+      <c r="E45" s="8" t="n">
         <v>7442</v>
       </c>
-      <c r="F45" s="19" t="n">
+      <c r="F45" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="G45" s="19" t="n">
+      <c r="G45" s="20" t="n">
         <v>129393</v>
       </c>
-      <c r="H45" s="20" t="n">
+      <c r="H45" s="21" t="n">
         <v>17.3868583714055</v>
       </c>
-      <c r="I45" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J45" s="22" t="n">
+      <c r="I45" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J45" s="23" t="n">
         <v>0.625148</v>
       </c>
-      <c r="K45" s="23" t="n">
+      <c r="K45" s="24" t="n">
         <v>155</v>
       </c>
-      <c r="L45" s="23" t="n">
+      <c r="L45" s="24" t="n">
         <v>129374</v>
       </c>
-      <c r="M45" s="24" t="n">
+      <c r="M45" s="25" t="n">
         <v>17.3843052942757</v>
       </c>
-      <c r="N45" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O45" s="26" t="n">
+      <c r="N45" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O45" s="27" t="n">
         <v>1.3044</v>
       </c>
-      <c r="P45" s="27" t="n">
+      <c r="P45" s="28" t="n">
         <v>24</v>
       </c>
-      <c r="Q45" s="27" t="n">
+      <c r="Q45" s="28" t="n">
         <v>126464</v>
       </c>
-      <c r="R45" s="28" t="n">
+      <c r="R45" s="29" t="n">
         <v>16.9932813759742</v>
       </c>
-      <c r="S45" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T45" s="30" t="n">
+      <c r="S45" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T45" s="31" t="n">
         <v>4.88782</v>
       </c>
-      <c r="U45" s="31" t="n">
+      <c r="U45" s="32" t="n">
         <v>14</v>
       </c>
       <c r="V45" s="32" t="n">
-        <v>17603</v>
+        <v>2005350</v>
       </c>
       <c r="W45" s="33" t="n">
-        <v>2.36535877452298</v>
+        <v>269.463853802741</v>
       </c>
       <c r="X45" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y45" s="35" t="n">
-        <v>2.77057</v>
+        <v>1.10339</v>
       </c>
       <c r="Z45" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="AA45" s="36" t="n">
-        <v>2005350</v>
-      </c>
-      <c r="AB45" s="37" t="n">
-        <v>269.463853802741</v>
-      </c>
-      <c r="AC45" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD45" s="39" t="n">
-        <v>1.10339</v>
+      <c r="AA45" s="37" t="n">
+        <v>17603</v>
+      </c>
+      <c r="AB45" s="38" t="n">
+        <v>2.36535877452298</v>
+      </c>
+      <c r="AC45" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD45" s="40" t="n">
+        <v>2.77057</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="10" t="n">
+      <c r="C46" s="11" t="n">
         <v>400</v>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="11" t="n">
         <v>55860</v>
       </c>
-      <c r="E46" s="7" t="n">
+      <c r="E46" s="8" t="n">
         <v>77719</v>
       </c>
-      <c r="F46" s="19" t="n">
+      <c r="F46" s="20" t="n">
         <v>41</v>
       </c>
-      <c r="G46" s="19" t="n">
+      <c r="G46" s="20" t="n">
         <v>544666</v>
       </c>
-      <c r="H46" s="20" t="n">
+      <c r="H46" s="21" t="n">
         <v>7.00814472651475</v>
       </c>
-      <c r="I46" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J46" s="22" t="n">
+      <c r="I46" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J46" s="23" t="n">
         <v>0.751079</v>
       </c>
-      <c r="K46" s="23" t="n">
+      <c r="K46" s="24" t="n">
         <v>438</v>
       </c>
-      <c r="L46" s="23" t="n">
+      <c r="L46" s="24" t="n">
         <v>542865</v>
       </c>
-      <c r="M46" s="24" t="n">
+      <c r="M46" s="25" t="n">
         <v>6.98497149989063</v>
       </c>
-      <c r="N46" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O46" s="26" t="n">
+      <c r="N46" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O46" s="27" t="n">
         <v>1.86288</v>
       </c>
-      <c r="P46" s="27" t="n">
+      <c r="P46" s="28" t="n">
         <v>71</v>
       </c>
-      <c r="Q46" s="27" t="n">
+      <c r="Q46" s="28" t="n">
         <v>527156</v>
       </c>
-      <c r="R46" s="28" t="n">
+      <c r="R46" s="29" t="n">
         <v>6.78284589353955</v>
       </c>
-      <c r="S46" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T46" s="30" t="n">
+      <c r="S46" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T46" s="31" t="n">
         <v>19.2329</v>
       </c>
-      <c r="U46" s="31" t="n">
+      <c r="U46" s="32" t="n">
         <v>41</v>
       </c>
       <c r="V46" s="32" t="n">
-        <v>152488</v>
+        <v>2806330</v>
       </c>
       <c r="W46" s="33" t="n">
-        <v>1.96204274373062</v>
+        <v>36.1086735547292</v>
       </c>
       <c r="X46" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y46" s="35" t="n">
-        <v>2.72922</v>
+        <v>1.3108</v>
       </c>
       <c r="Z46" s="36" t="n">
         <v>41</v>
       </c>
-      <c r="AA46" s="36" t="n">
-        <v>2806330</v>
-      </c>
-      <c r="AB46" s="37" t="n">
-        <v>36.1086735547292</v>
-      </c>
-      <c r="AC46" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD46" s="39" t="n">
-        <v>1.3108</v>
+      <c r="AA46" s="37" t="n">
+        <v>152488</v>
+      </c>
+      <c r="AB46" s="38" t="n">
+        <v>1.96204274373062</v>
+      </c>
+      <c r="AC46" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD46" s="40" t="n">
+        <v>2.72922</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C47" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="D47" s="5" t="n">
+      <c r="D47" s="6" t="n">
         <v>55860</v>
       </c>
-      <c r="E47" s="7" t="n">
+      <c r="E47" s="8" t="n">
         <v>44155</v>
       </c>
-      <c r="F47" s="19" t="n">
+      <c r="F47" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="G47" s="19" t="n">
+      <c r="G47" s="20" t="n">
         <v>413269</v>
       </c>
-      <c r="H47" s="20" t="n">
+      <c r="H47" s="21" t="n">
         <v>9.35950628467897</v>
       </c>
-      <c r="I47" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J47" s="22" t="n">
+      <c r="I47" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J47" s="23" t="n">
         <v>0.596125</v>
       </c>
-      <c r="K47" s="23" t="n">
+      <c r="K47" s="24" t="n">
         <v>383</v>
       </c>
-      <c r="L47" s="23" t="n">
+      <c r="L47" s="24" t="n">
         <v>413269</v>
       </c>
-      <c r="M47" s="24" t="n">
+      <c r="M47" s="25" t="n">
         <v>9.35950628467897</v>
       </c>
-      <c r="N47" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O47" s="26" t="n">
+      <c r="N47" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O47" s="27" t="n">
         <v>1.44468</v>
       </c>
-      <c r="P47" s="27" t="n">
+      <c r="P47" s="28" t="n">
         <v>31</v>
       </c>
-      <c r="Q47" s="27" t="n">
+      <c r="Q47" s="28" t="n">
         <v>413145</v>
       </c>
-      <c r="R47" s="28" t="n">
+      <c r="R47" s="29" t="n">
         <v>9.35669799569698</v>
       </c>
-      <c r="S47" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T47" s="30" t="n">
+      <c r="S47" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T47" s="31" t="n">
         <v>0.720634</v>
       </c>
-      <c r="U47" s="31" t="n">
+      <c r="U47" s="32" t="n">
         <v>30</v>
       </c>
       <c r="V47" s="32" t="n">
-        <v>82646</v>
+        <v>2809190</v>
       </c>
       <c r="W47" s="33" t="n">
-        <v>1.87172460649983</v>
+        <v>63.6211074623486</v>
       </c>
       <c r="X47" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y47" s="35" t="n">
-        <v>3.1941</v>
+        <v>1.31728</v>
       </c>
       <c r="Z47" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="AA47" s="36" t="n">
-        <v>2809190</v>
-      </c>
-      <c r="AB47" s="37" t="n">
-        <v>63.6211074623486</v>
-      </c>
-      <c r="AC47" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD47" s="39" t="n">
-        <v>1.31728</v>
+      <c r="AA47" s="37" t="n">
+        <v>82646</v>
+      </c>
+      <c r="AB47" s="38" t="n">
+        <v>1.87172460649983</v>
+      </c>
+      <c r="AC47" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD47" s="40" t="n">
+        <v>3.1941</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="10" t="n">
+      <c r="C48" s="11" t="n">
         <v>400</v>
       </c>
-      <c r="D48" s="10" t="n">
+      <c r="D48" s="11" t="n">
         <v>55860</v>
       </c>
-      <c r="E48" s="7" t="n">
+      <c r="E48" s="8" t="n">
         <v>24727</v>
       </c>
-      <c r="F48" s="19" t="n">
+      <c r="F48" s="20" t="n">
         <v>29</v>
       </c>
-      <c r="G48" s="19" t="n">
+      <c r="G48" s="20" t="n">
         <v>338061</v>
       </c>
-      <c r="H48" s="20" t="n">
+      <c r="H48" s="21" t="n">
         <v>13.6717353500222</v>
       </c>
-      <c r="I48" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J48" s="22" t="n">
+      <c r="I48" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J48" s="23" t="n">
         <v>0.817195</v>
       </c>
-      <c r="K48" s="23" t="n">
+      <c r="K48" s="24" t="n">
         <v>335</v>
       </c>
-      <c r="L48" s="23" t="n">
+      <c r="L48" s="24" t="n">
         <v>330338</v>
       </c>
-      <c r="M48" s="24" t="n">
+      <c r="M48" s="25" t="n">
         <v>13.3594046993165</v>
       </c>
-      <c r="N48" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O48" s="26" t="n">
+      <c r="N48" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O48" s="27" t="n">
         <v>1.79784</v>
       </c>
-      <c r="P48" s="27" t="n">
+      <c r="P48" s="28" t="n">
         <v>44</v>
       </c>
-      <c r="Q48" s="27" t="n">
+      <c r="Q48" s="28" t="n">
         <v>305961</v>
       </c>
-      <c r="R48" s="28" t="n">
+      <c r="R48" s="29" t="n">
         <v>12.3735592671978</v>
       </c>
-      <c r="S48" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T48" s="30" t="n">
+      <c r="S48" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T48" s="31" t="n">
         <v>5.82492</v>
       </c>
-      <c r="U48" s="31" t="n">
+      <c r="U48" s="32" t="n">
         <v>29</v>
       </c>
       <c r="V48" s="32" t="n">
-        <v>77215</v>
+        <v>2801920</v>
       </c>
       <c r="W48" s="33" t="n">
-        <v>3.1226998827193</v>
+        <v>113.314190965342</v>
       </c>
       <c r="X48" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y48" s="35" t="n">
-        <v>2.4975</v>
+        <v>1.38412</v>
       </c>
       <c r="Z48" s="36" t="n">
         <v>29</v>
       </c>
-      <c r="AA48" s="36" t="n">
-        <v>2801920</v>
-      </c>
-      <c r="AB48" s="37" t="n">
-        <v>113.314190965342</v>
-      </c>
-      <c r="AC48" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD48" s="39" t="n">
-        <v>1.38412</v>
+      <c r="AA48" s="37" t="n">
+        <v>77215</v>
+      </c>
+      <c r="AB48" s="38" t="n">
+        <v>3.1226998827193</v>
+      </c>
+      <c r="AC48" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD48" s="40" t="n">
+        <v>2.4975</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C49" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="D49" s="5" t="n">
+      <c r="D49" s="6" t="n">
         <v>250500</v>
       </c>
-      <c r="E49" s="7" t="n">
+      <c r="E49" s="8" t="n">
         <v>10661</v>
       </c>
-      <c r="F49" s="19" t="n">
+      <c r="F49" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="G49" s="19" t="n">
+      <c r="G49" s="20" t="n">
         <v>376843</v>
       </c>
-      <c r="H49" s="20" t="n">
+      <c r="H49" s="21" t="n">
         <v>35.3478097739424</v>
       </c>
-      <c r="I49" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J49" s="22" t="n">
+      <c r="I49" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J49" s="23" t="n">
         <v>8.07226</v>
       </c>
-      <c r="K49" s="23" t="n">
+      <c r="K49" s="24" t="n">
         <v>243</v>
       </c>
-      <c r="L49" s="23" t="n">
+      <c r="L49" s="24" t="n">
         <v>376798</v>
       </c>
-      <c r="M49" s="24" t="n">
+      <c r="M49" s="25" t="n">
         <v>35.3435887815402</v>
       </c>
-      <c r="N49" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O49" s="26" t="n">
+      <c r="N49" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O49" s="27" t="n">
         <v>11.4963</v>
       </c>
-      <c r="P49" s="27" t="n">
+      <c r="P49" s="28" t="n">
         <v>22</v>
       </c>
-      <c r="Q49" s="27" t="n">
+      <c r="Q49" s="28" t="n">
         <v>376016</v>
       </c>
-      <c r="R49" s="28" t="n">
+      <c r="R49" s="29" t="n">
         <v>35.2702373135728</v>
       </c>
-      <c r="S49" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T49" s="30" t="n">
+      <c r="S49" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T49" s="31" t="n">
         <v>24.7493</v>
       </c>
-      <c r="U49" s="31" t="n">
+      <c r="U49" s="32" t="n">
         <v>16</v>
       </c>
       <c r="V49" s="32" t="n">
-        <v>23682</v>
+        <v>12564000</v>
       </c>
       <c r="W49" s="33" t="n">
-        <v>2.22136760153832</v>
+        <v>1178.50107869806</v>
       </c>
       <c r="X49" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y49" s="35" t="n">
-        <v>41.0504</v>
+        <v>10.7742</v>
       </c>
       <c r="Z49" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="AA49" s="36" t="n">
-        <v>12564000</v>
-      </c>
-      <c r="AB49" s="37" t="n">
-        <v>1178.50107869806</v>
-      </c>
-      <c r="AC49" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD49" s="39" t="n">
-        <v>10.7742</v>
+      <c r="AA49" s="37" t="n">
+        <v>23682</v>
+      </c>
+      <c r="AB49" s="38" t="n">
+        <v>2.22136760153832</v>
+      </c>
+      <c r="AC49" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD49" s="40" t="n">
+        <v>41.0504</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C50" s="10" t="n">
+      <c r="C50" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D50" s="10" t="n">
+      <c r="D50" s="11" t="n">
         <v>13868</v>
       </c>
-      <c r="E50" s="7" t="n">
+      <c r="E50" s="8" t="n">
         <v>16398</v>
       </c>
-      <c r="F50" s="19" t="n">
+      <c r="F50" s="20" t="n">
         <v>51</v>
       </c>
-      <c r="G50" s="19" t="n">
+      <c r="G50" s="20" t="n">
         <v>298303</v>
       </c>
-      <c r="H50" s="20" t="n">
+      <c r="H50" s="21" t="n">
         <v>18.1914257836322</v>
       </c>
-      <c r="I50" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J50" s="22" t="n">
+      <c r="I50" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J50" s="23" t="n">
         <v>0.115874</v>
       </c>
-      <c r="K50" s="23" t="n">
+      <c r="K50" s="24" t="n">
         <v>307</v>
       </c>
-      <c r="L50" s="23" t="n">
+      <c r="L50" s="24" t="n">
         <v>262802</v>
       </c>
-      <c r="M50" s="24" t="n">
+      <c r="M50" s="25" t="n">
         <v>16.0264666422735</v>
       </c>
-      <c r="N50" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O50" s="26" t="n">
+      <c r="N50" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O50" s="27" t="n">
         <v>0.431782</v>
       </c>
-      <c r="P50" s="27" t="n">
+      <c r="P50" s="28" t="n">
         <v>117</v>
       </c>
-      <c r="Q50" s="27" t="n">
+      <c r="Q50" s="28" t="n">
         <v>217339</v>
       </c>
-      <c r="R50" s="28" t="n">
+      <c r="R50" s="29" t="n">
         <v>13.2539943895597</v>
       </c>
-      <c r="S50" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T50" s="30" t="n">
+      <c r="S50" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T50" s="31" t="n">
         <v>8.96637</v>
       </c>
-      <c r="U50" s="31" t="n">
+      <c r="U50" s="32" t="n">
         <v>51</v>
       </c>
       <c r="V50" s="32" t="n">
-        <v>208980</v>
+        <v>696536</v>
       </c>
       <c r="W50" s="33" t="n">
-        <v>12.7442371020856</v>
+        <v>42.4768874252958</v>
       </c>
       <c r="X50" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y50" s="35" t="n">
-        <v>0.573736</v>
+        <v>0.278238</v>
       </c>
       <c r="Z50" s="36" t="n">
         <v>51</v>
       </c>
-      <c r="AA50" s="36" t="n">
-        <v>696536</v>
-      </c>
-      <c r="AB50" s="37" t="n">
-        <v>42.4768874252958</v>
-      </c>
-      <c r="AC50" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD50" s="39" t="n">
-        <v>0.278238</v>
+      <c r="AA50" s="37" t="n">
+        <v>208980</v>
+      </c>
+      <c r="AB50" s="38" t="n">
+        <v>12.7442371020856</v>
+      </c>
+      <c r="AC50" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD50" s="40" t="n">
+        <v>0.573736</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C51" s="6" t="n">
         <v>400</v>
       </c>
-      <c r="D51" s="5" t="n">
+      <c r="D51" s="6" t="n">
         <v>39984</v>
       </c>
-      <c r="E51" s="7" t="n">
+      <c r="E51" s="8" t="n">
         <v>8298</v>
       </c>
-      <c r="F51" s="19" t="n">
+      <c r="F51" s="20" t="n">
         <v>61</v>
       </c>
-      <c r="G51" s="19" t="n">
+      <c r="G51" s="20" t="n">
         <v>507447</v>
       </c>
-      <c r="H51" s="20" t="n">
+      <c r="H51" s="21" t="n">
         <v>61.1529284164859</v>
       </c>
-      <c r="I51" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J51" s="22" t="n">
+      <c r="I51" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J51" s="23" t="n">
         <v>0.765061</v>
       </c>
-      <c r="K51" s="23" t="n">
+      <c r="K51" s="24" t="n">
         <v>369</v>
       </c>
-      <c r="L51" s="23" t="n">
+      <c r="L51" s="24" t="n">
         <v>454321</v>
       </c>
-      <c r="M51" s="24" t="n">
+      <c r="M51" s="25" t="n">
         <v>54.7506628103157</v>
       </c>
-      <c r="N51" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O51" s="26" t="n">
+      <c r="N51" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O51" s="27" t="n">
         <v>1.83038</v>
       </c>
-      <c r="P51" s="27" t="n">
+      <c r="P51" s="28" t="n">
         <v>299</v>
       </c>
-      <c r="Q51" s="27" t="n">
+      <c r="Q51" s="28" t="n">
         <v>332167</v>
       </c>
-      <c r="R51" s="28" t="n">
+      <c r="R51" s="29" t="n">
         <v>40.029766208725</v>
       </c>
-      <c r="S51" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T51" s="30" t="n">
+      <c r="S51" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T51" s="31" t="n">
         <v>646.169</v>
       </c>
-      <c r="U51" s="31" t="n">
+      <c r="U51" s="32" t="n">
         <v>61</v>
       </c>
       <c r="V51" s="32" t="n">
-        <v>309987</v>
+        <v>1999800</v>
       </c>
       <c r="W51" s="33" t="n">
-        <v>37.3568329718004</v>
+        <v>240.997830802603</v>
       </c>
       <c r="X51" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y51" s="35" t="n">
-        <v>2.39253</v>
+        <v>1.11016</v>
       </c>
       <c r="Z51" s="36" t="n">
         <v>61</v>
       </c>
-      <c r="AA51" s="36" t="n">
-        <v>1999800</v>
-      </c>
-      <c r="AB51" s="37" t="n">
-        <v>240.997830802603</v>
-      </c>
-      <c r="AC51" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD51" s="39" t="n">
-        <v>1.11016</v>
+      <c r="AA51" s="37" t="n">
+        <v>309987</v>
+      </c>
+      <c r="AB51" s="38" t="n">
+        <v>37.3568329718004</v>
+      </c>
+      <c r="AC51" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD51" s="40" t="n">
+        <v>2.39253</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C52" s="10" t="n">
+      <c r="C52" s="11" t="n">
         <v>400</v>
       </c>
-      <c r="D52" s="10" t="n">
+      <c r="D52" s="11" t="n">
         <v>55869</v>
       </c>
-      <c r="E52" s="7" t="n">
+      <c r="E52" s="8" t="n">
         <v>22791</v>
       </c>
-      <c r="F52" s="19" t="n">
+      <c r="F52" s="20" t="n">
         <v>90</v>
       </c>
-      <c r="G52" s="19" t="n">
+      <c r="G52" s="20" t="n">
         <v>1082260</v>
       </c>
-      <c r="H52" s="20" t="n">
+      <c r="H52" s="21" t="n">
         <v>47.4862884471941</v>
       </c>
-      <c r="I52" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="J52" s="22" t="n">
+      <c r="I52" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J52" s="23" t="n">
         <v>0.612586</v>
       </c>
-      <c r="K52" s="23" t="n">
+      <c r="K52" s="24" t="n">
         <v>544</v>
       </c>
-      <c r="L52" s="23" t="n">
+      <c r="L52" s="24" t="n">
         <v>940970</v>
       </c>
-      <c r="M52" s="24" t="n">
+      <c r="M52" s="25" t="n">
         <v>41.2869115001536</v>
       </c>
-      <c r="N52" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O52" s="26" t="n">
+      <c r="N52" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="O52" s="27" t="n">
         <v>2.53527</v>
       </c>
-      <c r="P52" s="27" t="n">
+      <c r="P52" s="28" t="n">
         <v>232</v>
       </c>
-      <c r="Q52" s="27" t="n">
+      <c r="Q52" s="28" t="n">
         <v>757685</v>
       </c>
-      <c r="R52" s="28" t="n">
+      <c r="R52" s="29" t="n">
         <v>33.2449212408407</v>
       </c>
-      <c r="S52" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="T52" s="30" t="n">
+      <c r="S52" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="T52" s="31" t="n">
         <v>128.633</v>
       </c>
-      <c r="U52" s="31" t="n">
+      <c r="U52" s="32" t="n">
         <v>90</v>
       </c>
       <c r="V52" s="32" t="n">
-        <v>673405</v>
+        <v>2804940</v>
       </c>
       <c r="W52" s="33" t="n">
-        <v>29.546970295292</v>
+        <v>123.072265367908</v>
       </c>
       <c r="X52" s="34" t="s">
         <v>78</v>
       </c>
       <c r="Y52" s="35" t="n">
-        <v>2.68095</v>
+        <v>1.34067</v>
       </c>
       <c r="Z52" s="36" t="n">
         <v>90</v>
       </c>
-      <c r="AA52" s="36" t="n">
-        <v>2804940</v>
-      </c>
-      <c r="AB52" s="37" t="n">
-        <v>123.072265367908</v>
-      </c>
-      <c r="AC52" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD52" s="39" t="n">
-        <v>1.34067</v>
+      <c r="AA52" s="37" t="n">
+        <v>673405</v>
+      </c>
+      <c r="AB52" s="38" t="n">
+        <v>29.546970295292</v>
+      </c>
+      <c r="AC52" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD52" s="40" t="n">
+        <v>2.68095</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AD52"/>
+  <autoFilter ref="A4:Y52"/>
   <mergeCells count="11">
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:Y1"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
